--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,89 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dong MY\Desktop\euraxess-tracker\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66A3E29-4525-4834-B909-4F362983E4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Jobs" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>First Seen</t>
-  </si>
-  <si>
-    <t>Posted</t>
-  </si>
-  <si>
-    <t>Deadline</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Organization</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Research Field</t>
-  </si>
-  <si>
-    <t>Researcher Profile</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Matched Keyword</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -102,24 +50,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -407,60 +414,1738 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="50" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>First Seen</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Research Field</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Researcher Profile</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Matched Keyword</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>University of Minho</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ANNOUNCEMENT FOR THE AWARD OF A RESEARCH FELLOWSHIP/IPC/SIMATRIX/MCN/17/2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Engineering » Materials engineering</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446046</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FEUP</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FEUP - Research Grant  - ST-e.Biofilm_M3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Engineering Engineering » Biomedical engineering Engineering » Other</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446045</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2 Jul 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nova School of Business and Economics</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nova SBE/BI/2026/08 - Research Fellowship – Junior Data &amp; AI Consultant - Project “Social Database”</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446042</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>31 Jul 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Institute of Public Health University of Porto</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>POSTDOCTORAL RESEARCH SCHOLARSHIP FOR HOLDERS OF A DOCTORAL DEGREE, UNDER THE "SHIELD-HMP" PROJECT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2) Established Researcher (R3) Leading Researcher (R4)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446044</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 - 00:00 (Atlantic/Reykjavik)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Reykjavik University</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PhD student – project “On the implementation of ensemble feature selection and its application to stock market prediction”</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Computer science » Informatics</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446041</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14 Jul 2026 - 14:00 (Europe/Rome)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Roma Tre</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PhD position: The large laboratory test site experiment to estimate the dielectric properties of the ice/ocean interface</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446038</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FCiências.ID</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BSc Research Technician Recruitment (Research Technician) #5320</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Environmental science » Other Biological sciences » Biology</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446040</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2 Jul 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Instituto de Telecomunicações</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Research Scholarship (“Bolsa de Investigação”) - BI/ Nº2026/00063</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Engineering » Other</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446035</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19 Jul 2026 - 23:59 (Europe/Paris)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Le Mans Université</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Postdoctoral researcher in palaeoglaciology and artificial intelligence</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Geosciences Communication sciences</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446039</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28 Jun 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Instituto Politécnico de Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bolsa de investigação - BI_01_2026_RISE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446036</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1 Jul 2026 - 23:59 (Europe/Andorra)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fundació Hospital Universitari Vall d'Hebron- Institut de recerca</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Research Assistant (Diabetes and Metabolism Research Group)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Biological sciences » Biology</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Other Profession</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446034</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1 Jul 2026 - 23:59 (Europe/Andorra)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fundació Hospital Universitari Vall d'Hebron- Institut de recerca</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Research Assistant (Diabetes and Metabolism Research Group)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Biological sciences » Biology</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Other Profession</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446032</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20 Jul 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Institute for bioengineering of Catalonia, IBEC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IBEC Director</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Biological sciences » Biological engineering</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Other Profession</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446031</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1 Jul 2026 - 23:59 (Europe/Andorra)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fundació Hospital Universitari Vall d'Hebron- Institut de recerca</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Clinical Researcher (Cardiovascular Diseases Research Group)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Biological sciences » Biology</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Other Profession</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446030</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1 Jul 2026 - 23:59 (Europe/Andorra)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fundació Hospital Universitari Vall d'Hebron- Institut de recerca</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Predoctoral Researcher (Molecular Medical Imaging)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Biological sciences » Biology</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446027</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6 Jul 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ASSOCIAÇÃO BIOPOLIS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Research Grant (BI)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Biological sciences » Biology</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446029</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Universitat Politècnica de València</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Call for a public offer for the recruitment of Researching staff linked to Universitat Politècnica de València (UPV)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Economics » Administrative sciences Economics</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Universitat Politècnica de València</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Call for a public offer for the recruitment of Researching staff linked to Universitat Politècnica de València (UPV)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Technology » Biotechnology</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>27 Jul 2026 - 23:59 (Europe/Lisbon)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Faculdade de Ciências Sociais e Humanas</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Call for 2 Research Grant for Master’s degree (BI Mestre CHAM)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446028</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>28 Jun 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Instituto de Investigación Sanitaria del Princiapdo de Asturias</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Postdoctoral Researcher to join Bone Metabolism research group</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Biological sciences</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446023</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Universitat Politècnica de València</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Call for a public offer for the recruitment of Researching staff linked to Universitat Politècnica de València (UPV)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Computer science</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446021</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>18 Jul 2026 - 00:00 (Europe/Prague)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kazimierz Wielki University in Bydgoszcz</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Assistant for teaching</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Universitat Politècnica de València</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Call for a public offer for the recruitment of Researching staff linked to Universitat Politècnica de València (UPV)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446020</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>30 Jul 2026 - 15:30 (Europe/Warsaw)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Lublin University of Technology</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Assistant in the group of research and teaching staff at the Department of Contemporary Architecture</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446022</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Universitat Politècnica de València</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Call for a public offer for the recruitment of Researching staff linked to Universitat Politècnica de València (UPV)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Engineering » Industrial engineering Technology » Industrial technology</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446019</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Universitat Politècnica de València</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Call for a public offer for the recruitment of Researching staff linked to Universitat Politècnica de València (UPV)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Arts</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446018</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3 Jul 2026 - 23:59 (Europe/Madrid)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Universitat Politècnica de València</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Call for a public offer for the recruitment of Researching staff linked to Universitat Politècnica de València (UPV)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Technology » Telecommunications technology</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446017</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>31 Jul 2026 - 23:59 (Europe/Berlin)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>University of Rostock</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Professorship (W3) for Service Management</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Management sciences » Other</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Established Researcher (R3) Leading Researcher (R4)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446016</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>18 June 2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21 Jul 2026 - 15:30 (Europe/Warsaw)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Lublin University of Technology</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Assistant in the group of research and teaching staff at the Department of Finance and Accounting</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Economics » Financial science Economics » Management studies</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>phd position</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/446014</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -495,37 +495,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>16 Jul 2026 - 14:34 (UTC)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PhD in Simulation-integrated strategy for polymers in integrated circuit packaging</t>
+          <t>Doctoral Researcher - CAR T Cell Therapy Development</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering Engineering » Mechanical engineering</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -545,44 +545,44 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443230</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446642</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>17 Jul 2026 - 06:33 (UTC)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PhD in Flexibility Services from Electrified Process Industry: A Focus on Steam-Heated Processes</t>
+          <t>PhD position in “Molecular Microbial Ecology focusing on phage-host interactions” (x/d/f/m)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Process engineering</t>
+          <t>Environmental science</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -602,49 +602,49 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443214</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446643</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3 Aug 2026 - 21:59 (UTC)</t>
+          <t>12 Jul 2026 - 21:00 (UTC)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Postdoc Safe Waterborne Digital Systems</t>
+          <t>Postdoctoral Researcher (m/f/d) Self-Driving Lab for the Discovery of Novel Catalyst Materials</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Maritime engineering</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -654,54 +654,54 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443221</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446644</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PhD in AI-driven Fair Energy Curtailment Policies</t>
+          <t>Postdoc (Physics) – ³He and neutron polarization methods</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Electrical engineering</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -711,54 +711,54 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443208</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446645</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Postdoc Tx/Rx Isolation Measurements of FMCW radar using a reverberation chamber (TRIM)</t>
+          <t>PhD Position - Active Matter and Machine Learning</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Electronic engineering</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -768,54 +768,54 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Automotive Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443225</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446646</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28 Jun 2026 - 21:59 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PhD Position on Strengthening Mortgage Portfolio Resilience to Physical Climate Risks</t>
+          <t>Postdoctoral Researcher in Quantum Algorithms</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Economics » Environmental economics Economics » Financial science Engineering » Civil engineering Engineering » Simulation engineering</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -825,54 +825,54 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443209</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446647</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Privacy-Preserving AI and Knowledge Graphs for Energy Digital Twins</t>
+          <t>Student Research Assistant – Polymer &amp; Membrane Materials for Next Generation Energy Technologies</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Computer science » Programming</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443229</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446648</t>
         </is>
       </c>
     </row>
@@ -899,37 +899,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8 May 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Professor in Chemical Engineering</t>
+          <t>PhD in Simulation-integrated strategy for polymers in integrated circuit packaging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Engineering » Chemical engineering</t>
+          <t>Engineering » Materials engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/434598</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443230</t>
         </is>
       </c>
     </row>
@@ -956,32 +956,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8 May 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4 Aug 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doctoral position on PFAS Pathways: Tracking “Forever Chemicals” through Soil–Groundwater Interfaces for Safer Water</t>
+          <t>PhD in Flexibility Services from Electrified Process Industry: A Focus on Steam-Heated Processes</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Soil science Chemistry » Analytical chemistry Chemistry » Other Computer science » Other Environmental science » Earth science Environmental science » Water science Environmental science » Other</t>
+          <t>Engineering » Electrical engineering Engineering » Process engineering</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/434621</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443214</t>
         </is>
       </c>
     </row>
@@ -1013,37 +1013,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8 June 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>3 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher (f_m_x) – Adaptive Digital Twin Prototypes for EGS Systems</t>
+          <t>Postdoc Safe Waterborne Digital Systems</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geosciences</t>
+          <t>Engineering » Control engineering Engineering » Maritime engineering</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443018</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443221</t>
         </is>
       </c>
     </row>
@@ -1070,32 +1070,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8 June 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>8 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PhD Thesis - In situ TEM of Coulomb phase excitation in artificial spin ice matter</t>
+          <t>PhD in AI-driven Fair Energy Curtailment Policies</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Engineering » Control engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443014</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443208</t>
         </is>
       </c>
     </row>
@@ -1127,37 +1127,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8 June 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Engineer for Laboratory Automation – AI Driven Photovoltaic Research</t>
+          <t>Postdoc Tx/Rx Isolation Measurements of FMCW radar using a reverberation chamber (TRIM)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Engineering » Electrical engineering Engineering » Electronic engineering</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Automotive Control</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443028</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443225</t>
         </is>
       </c>
     </row>
@@ -1184,32 +1184,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8 June 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4 Jul 2026 - 22:00 (UTC)</t>
+          <t>28 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PhD Student (f/m/d) Upscaling Particle-Based Separation Models: Bridging Laboratory and Industrial Flotation Processes / Completed university studies (Master/Diploma) in the field of Chemical/Metallurgical/(Mineral) Process Engineering …</t>
+          <t>PhD Position on Strengthening Mortgage Portfolio Resilience to Physical Climate Risks</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Economics » Environmental economics Economics » Financial science Engineering » Civil engineering Engineering » Simulation engineering</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443042</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443209</t>
         </is>
       </c>
     </row>
@@ -1241,37 +1241,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8 June 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>26 Jun 2026 - 04:11 (UTC)</t>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Postdoc in "Human Decisions in Environmental Systems" (f/d/m/x) (HIPP 27.4)</t>
+          <t>Privacy-Preserving AI and Knowledge Graphs for Energy Digital Twins</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Environmental science</t>
+          <t>Computer science » Programming</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443030</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443229</t>
         </is>
       </c>
     </row>
@@ -1298,37 +1298,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8 June 2026</t>
+          <t>8 May 2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>26 Jun 2026 - 04:24 (UTC)</t>
+          <t>22 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Postdoc in "Science Narratives" (m/d/f/x) (HIPP 27.5)</t>
+          <t>Professor in Chemical Engineering</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Environmental science</t>
+          <t>Engineering » Chemical engineering</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>Leading Researcher (R4)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443032</t>
+          <t>https://euraxess.ec.europa.eu/jobs/434598</t>
         </is>
       </c>
     </row>
@@ -1355,17 +1355,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7 May 2026</t>
+          <t>8 May 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20 Jun 2026 - 21:59 (UTC)</t>
+          <t>4 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Postdoc in optical quantum networks</t>
+          <t>Doctoral position on PFAS Pathways: Tracking “Forever Chemicals” through Soil–Groundwater Interfaces for Safer Water</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Engineering » Other Physics » Optics Physics » Quantum mechanics Physics » Other</t>
+          <t>Agricultural sciences » Soil science Chemistry » Analytical chemistry Chemistry » Other Computer science » Other Environmental science » Earth science Environmental science » Water science Environmental science » Other</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/434335</t>
+          <t>https://euraxess.ec.europa.eu/jobs/434621</t>
         </is>
       </c>
     </row>
@@ -1412,37 +1412,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7 February 2026</t>
+          <t>8 June 2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Postdoc on Continuous Optical Clocks</t>
+          <t>Postdoctoral Researcher (f_m_x) – Adaptive Digital Twin Prototypes for EGS Systems</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Physics » Optics Physics » Quantum mechanics</t>
+          <t>Geosciences</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/408015</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443018</t>
         </is>
       </c>
     </row>
@@ -1469,32 +1469,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6 June 2026</t>
+          <t>8 June 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doctoral student in Grid Impact Assessment of Optimized Energy Communities</t>
+          <t>PhD Thesis - In situ TEM of Coulomb phase excitation in artificial spin ice matter</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Engineering » Other Technology » Energy technology Technology » Environmental technology</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442914</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443014</t>
         </is>
       </c>
     </row>
@@ -1526,37 +1526,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6 June 2026</t>
+          <t>8 June 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15 Aug 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Head of Analytical Laboratories/Senior MC-ICP-MS Specialist in Isotope Geochemistry</t>
+          <t>Engineer for Laboratory Automation – AI Driven Photovoltaic Research</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chemistry » Analytical chemistry Chemistry » Other Environmental science » Earth science Environmental science » Other</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442916</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443028</t>
         </is>
       </c>
     </row>
@@ -1583,32 +1583,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6 June 2026</t>
+          <t>8 June 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3 Sep 2026 - 21:59 (UTC)</t>
+          <t>4 Jul 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PhD position in Multi-State Programmable Robotic Matter</t>
+          <t>PhD Student (f/m/d) Upscaling Particle-Based Separation Models: Bridging Laboratory and Industrial Flotation Processes / Completed university studies (Master/Diploma) in the field of Chemical/Metallurgical/(Mineral) Process Engineering …</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chemistry » Other Engineering » Chemical engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442917</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443042</t>
         </is>
       </c>
     </row>
@@ -1640,37 +1640,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6 June 2026</t>
+          <t>8 June 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3 Sep 2026 - 21:59 (UTC)</t>
+          <t>26 Jun 2026 - 04:11 (UTC)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PhD position in Biohybrid Robotics</t>
+          <t>Postdoc in "Human Decisions in Environmental Systems" (f/d/m/x) (HIPP 27.4)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Biological sciences » Other Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Systems engineering Engineering » Other</t>
+          <t>Environmental science</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442922</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443030</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6 February 2026</t>
+          <t>8 June 2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>26 Jun 2026 - 04:24 (UTC)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Postdoc on Quantum Simulation &amp; Computing with Single Sr Atoms in Optical Tweezers</t>
+          <t>Postdoc in "Science Narratives" (m/d/f/x) (HIPP 27.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Physics » Optics Physics » Quantum mechanics</t>
+          <t>Environmental science</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/407551</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443032</t>
         </is>
       </c>
     </row>
@@ -1754,37 +1754,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>7 May 2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
+          <t>20 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paul Scherrer Institut Villigen</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PhD Student in Probabilistic Modelling of Severe Nuclear Accident Risk (Index-Nr. 4103-28180)</t>
+          <t>Postdoc in optical quantum networks</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Engineering » Nuclear engineering Engineering » Chemical engineering Engineering » Mechanical engineering</t>
+          <t>Computer science » Other Engineering » Electrical engineering Engineering » Other Physics » Optics Physics » Quantum mechanics Physics » Other</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/433719</t>
+          <t>https://euraxess.ec.europa.eu/jobs/434335</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>7 February 2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1826,17 +1826,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Postdoc Real-World Testing of Future In-Vehicle Touchscreens</t>
+          <t>Postdoc on Continuous Optical Clocks</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Mechanical engineering</t>
+          <t>Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442540</t>
+          <t>https://euraxess.ec.europa.eu/jobs/408015</t>
         </is>
       </c>
     </row>
@@ -1868,32 +1868,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>6 June 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PhD Position Delocalized Quantum Magnetism in Atomic Spin Assemblies</t>
+          <t>Doctoral student in Grid Impact Assessment of Optimized Energy Communities</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
+          <t>Engineering » Other Technology » Energy technology Technology » Environmental technology</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442548</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442914</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>6 June 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1940,22 +1940,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PhD Position Spin-Wave Generation in Quantum Materials</t>
+          <t>Head of Analytical Laboratories/Senior MC-ICP-MS Specialist in Isotope Geochemistry</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
+          <t>Chemistry » Analytical chemistry Chemistry » Other Environmental science » Earth science Environmental science » Other</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442549</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442916</t>
         </is>
       </c>
     </row>
@@ -1982,17 +1982,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>6 June 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 21:59 (UTC)</t>
+          <t>3 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doctoral student in SiC bipolar devices for power electronics</t>
+          <t>PhD position in Multi-State Programmable Robotic Matter</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Other Technology » Energy technology</t>
+          <t>Chemistry » Other Engineering » Chemical engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442633</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442917</t>
         </is>
       </c>
     </row>
@@ -2039,17 +2039,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>6 June 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1 Sep 2026 - 21:59 (UTC)</t>
+          <t>3 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Postdoc in simulation model development for climate-neutral waterborne transport on coastal and inland waterways</t>
+          <t>PhD position in Biohybrid Robotics</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Engineering » Mechanical engineering Engineering » Systems engineering Engineering » Other Physics » Other Technology » Energy technology Technology » Environmental technology Technology » Transport technology</t>
+          <t>Biological sciences » Other Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Systems engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442646</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442922</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>6 February 2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2111,22 +2111,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PhD in Computer Architecture for Real-Time AI at the Edge</t>
+          <t>Postdoc on Quantum Simulation &amp; Computing with Single Sr Atoms in Optical Tweezers</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Computer science » Computer architecture Computer science » Computer hardware</t>
+          <t>Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442550</t>
+          <t>https://euraxess.ec.europa.eu/jobs/407551</t>
         </is>
       </c>
     </row>
@@ -2153,32 +2153,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Uppsala Universitet via MyNetwork</t>
+          <t>Paul Scherrer Institut Villigen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PhD student in Machine Learning with a focus on mathematical foundations of uncertainty quantification in deep learning</t>
+          <t>PhD Student in Probabilistic Modelling of Severe Nuclear Accident Risk (Index-Nr. 4103-28180)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Computer science Technology</t>
+          <t>Engineering » Nuclear engineering Engineering » Chemical engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442538</t>
+          <t>https://euraxess.ec.europa.eu/jobs/433719</t>
         </is>
       </c>
     </row>
@@ -2215,25 +2215,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7 Aug 2026 - 12:00 (UTC)</t>
+          <t>15 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Talentech</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Postdoc in stretchable fluid batteries for sustainable wearable electronics</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Postdoc Real-World Testing of Future In-Vehicle Touchscreens</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Engineering » Control engineering Engineering » Mechanical engineering</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Recognised Researcher (R2)</t>
@@ -2246,12 +2250,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442536</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442540</t>
         </is>
       </c>
     </row>
@@ -2268,27 +2272,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16 Jul 2026 - 23:19 (UTC)</t>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>myScience</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doctorante</t>
+          <t>PhD Position Delocalized Quantum Magnetism in Atomic Spin Assemblies</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pharmacological sciences Medical sciences</t>
+          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2303,12 +2307,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442537</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442548</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2329,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2340,17 +2344,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Assistant Professor on Network Science</t>
+          <t>PhD Position Spin-Wave Generation in Quantum Materials</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Engineering » Computer engineering Engineering » Electrical engineering</t>
+          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2360,12 +2364,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442547</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442549</t>
         </is>
       </c>
     </row>
@@ -2382,32 +2386,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15 Aug 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Assistant Professors in Language and AI Engineering</t>
+          <t>Doctoral student in SiC bipolar devices for power electronics</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Computer science Language sciences » Linguistics</t>
+          <t>Engineering » Electrical engineering Engineering » Other Technology » Energy technology</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2417,12 +2421,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442542</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442633</t>
         </is>
       </c>
     </row>
@@ -2434,37 +2438,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4 May 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
+          <t>1 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paul Scherrer Institut Villigen</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PhD Student in the Development of Models for Droplet Behaviour in PWRs (Index-Nr. 4103-27812)</t>
+          <t>Postdoc in simulation model development for climate-neutral waterborne transport on coastal and inland waterways</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Engineering » Mechanical engineering Engineering » Nuclear engineering Physics Mathematics » Applied mathematics</t>
+          <t>Engineering » Mechanical engineering Engineering » Systems engineering Engineering » Other Physics » Other Technology » Energy technology Technology » Environmental technology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2474,12 +2478,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/433442</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442646</t>
         </is>
       </c>
     </row>
@@ -2491,37 +2495,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Postdoc in LLM Agents for Research Automation</t>
+          <t>PhD in Computer Architecture for Real-Time AI at the Edge</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other</t>
+          <t>Computer science » Computer architecture Computer science » Computer hardware</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2531,12 +2535,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Automotive Control</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442359</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442550</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2552,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2563,22 +2567,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Uppsala Universitet via MyNetwork</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Post-doc in bio-fuel production using experiments and AI-assisted analysis</t>
+          <t>PhD student in Machine Learning with a focus on mathematical foundations of uncertainty quantification in deep learning</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chemistry » Other Computer science » Other Engineering » Chemical engineering Engineering » Other Technology » Energy technology</t>
+          <t>Computer science Technology</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2588,12 +2592,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442363</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442538</t>
         </is>
       </c>
     </row>
@@ -2605,37 +2609,33 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 12:00 (Europe/Berlin)</t>
+          <t>7 Aug 2026 - 12:00 (UTC)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Continuum Mechanics Group - TUM</t>
+          <t>Talentech</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Postdoc Position on Physics-informed Generative Modeling and Multiscale Learning (m/w/d)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Simulation engineering Engineering</t>
-        </is>
-      </c>
+          <t>Postdoc in stretchable fluid batteries for sustainable wearable electronics</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442500</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442536</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 13:12 (Europe/Berlin)</t>
+          <t>16 Jul 2026 - 23:19 (UTC)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Continuum Mechanics Group - TUM</t>
+          <t>myScience</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ph.D. Position on Physics-informed Generative Modeling and Multiscale Learning</t>
+          <t>Doctorante</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Simulation engineering Mathematics » Computational mathematics</t>
+          <t>Pharmacological sciences Medical sciences</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442498</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442537</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>24 Jun 2026 - 21:59 (UTC)</t>
+          <t>2 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2734,22 +2734,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Postdoctoral researcher Evaluating Methodologies for Urban Resilience</t>
+          <t>Assistant Professor on Network Science</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sociology » Urban sociology</t>
+          <t>Engineering » Computer engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442256</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442547</t>
         </is>
       </c>
     </row>
@@ -2776,37 +2776,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1 Sep 2026 - 21:59 (UTC)</t>
+          <t>15 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PhD Position in Infrastructure Intervention Effectiveness Analysis for Road Safety</t>
+          <t>Assistant Professors in Language and AI Engineering</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Architecture » Other Technology » Transport technology</t>
+          <t>Computer science Language sciences » Linguistics</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442360</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442542</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>4 May 2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1 Sep 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Paul Scherrer Institut Villigen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PhD Position in Vehicle Sensor and Remote Sensing Analysis for Road Safety</t>
+          <t>PhD Student in the Development of Models for Droplet Behaviour in PWRs (Index-Nr. 4103-27812)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Civil engineering Engineering » Other Environmental science » Earth science Technology » Transport technology</t>
+          <t>Engineering » Mechanical engineering Engineering » Nuclear engineering Physics Mathematics » Applied mathematics</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442361</t>
+          <t>https://euraxess.ec.europa.eu/jobs/433442</t>
         </is>
       </c>
     </row>
@@ -2890,37 +2890,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>31 October 2025</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>31 Dec 2029 - 23:59 (Europe/Berlin)</t>
+          <t>3 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Makino Europe GmbH</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Internship Industrial Research Metal Cutting Monitoring and Simulation</t>
+          <t>Postdoc in LLM Agents for Research Automation</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Engineering » Simulation engineering Engineering » Mechanical engineering</t>
+          <t>Computer science » Programming Computer science » Other</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/384615</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442359</t>
         </is>
       </c>
     </row>
@@ -2947,12 +2947,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>31 May 2026</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2962,22 +2962,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doctoral student in Electrical Engineering focusing on Machine Learning</t>
+          <t>Post-doc in bio-fuel production using experiments and AI-assisted analysis</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering</t>
+          <t>Chemistry » Other Computer science » Other Engineering » Chemical engineering Engineering » Other Technology » Energy technology</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441319</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442363</t>
         </is>
       </c>
     </row>
@@ -3004,37 +3004,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30 May 2026</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 12:00 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Continuum Mechanics Group - TUM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PhD position: aboveground-belowground linkages in beech masting dynamics - NIOO-KNAW - Wageningen</t>
+          <t>Postdoc Position on Physics-informed Generative Modeling and Multiscale Learning (m/w/d)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Simulation engineering Engineering</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441155</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442500</t>
         </is>
       </c>
     </row>
@@ -3061,37 +3061,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30 May 2026</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>25 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 13:12 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Continuum Mechanics Group - TUM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Junior Researcher Smart Charging &amp; Vehicle-to-Grid (V2G)</t>
+          <t>Ph.D. Position on Physics-informed Generative Modeling and Multiscale Learning</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering</t>
+          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Simulation engineering Mathematics » Computational mathematics</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441152</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442498</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3 June 2026</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 23:59 (Europe/Berlin)</t>
+          <t>24 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ruhr University Bochum</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Three-year Postdoc (m/f/d) in X-ray photoemission spectroscopy of lithium batteries (TV-L 13 100%)</t>
+          <t>Postdoctoral researcher Evaluating Methodologies for Urban Resilience</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering</t>
+          <t>Sociology » Urban sociology</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1) Recognised Researcher (R2) Established Researcher (R3) Leading Researcher (R4)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442179</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442256</t>
         </is>
       </c>
     </row>
@@ -3175,30 +3175,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3 June 2026</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>23 Jun 2026 - 12:00 (UTC)</t>
+          <t>1 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Talentech</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PhD in Plant Bioelectronics</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>PhD Position in Infrastructure Intervention Effectiveness Analysis for Road Safety</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Architecture » Other Technology » Transport technology</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>First Stage Researcher (R1)</t>
@@ -3211,12 +3215,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441871</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442360</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3232,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3 June 2026</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
+          <t>1 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3243,17 +3247,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Idiap Research Institute</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher: Trustworthy &amp; Privacy-Preserving Identity Technologies F/M</t>
+          <t>PhD Position in Vehicle Sensor and Remote Sensing Analysis for Road Safety</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Computer science</t>
+          <t>Computer science » Other Engineering » Civil engineering Engineering » Other Environmental science » Earth science Technology » Transport technology</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3273,7 +3277,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442142</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442361</t>
         </is>
       </c>
     </row>
@@ -3285,32 +3289,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3 June 2026</t>
+          <t>31 October 2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 21:59 (UTC)</t>
+          <t>31 Dec 2029 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Karolinska Institutet via Varbi</t>
+          <t>Makino Europe GmbH</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Assistant Professor in Data-Driven Cardiovascular Medicine</t>
+          <t>Internship Industrial Research Metal Cutting Monitoring and Simulation</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Medical sciences » Medicine</t>
+          <t>Engineering » Simulation engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3325,12 +3329,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Automotive Control</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441909</t>
+          <t>https://euraxess.ec.europa.eu/jobs/384615</t>
         </is>
       </c>
     </row>
@@ -3342,37 +3346,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3 June 2026</t>
+          <t>31 May 2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2 Aug 2026 - 21:59 (UTC)</t>
+          <t>22 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Assistant Professor In Formal Methods and Neuro-Symbolic AI</t>
+          <t>Doctoral student in Electrical Engineering focusing on Machine Learning</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Computer science » Autonomic computing Computer science » Cybernetics</t>
+          <t>Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3382,12 +3386,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441881</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441319</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3403,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 21:59 (UTC)</t>
+          <t>22 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3414,22 +3418,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Postdoc Recycling of Lithium Iron Phosphate Batteries</t>
+          <t>PhD position: aboveground-belowground linkages in beech masting dynamics - NIOO-KNAW - Wageningen</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Engineering » Chemical engineering Engineering » Process engineering</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3439,12 +3443,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440768</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441155</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3460,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>20 Jun 2026 - 22:00 (UTC)</t>
+          <t>25 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3471,22 +3475,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>University of Groningen via AcademicTransfer</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PhD position Sensors for Neuromorphic Touch in Adaptive Robotic Grasping</t>
+          <t>Junior Researcher Smart Charging &amp; Vehicle-to-Grid (V2G)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Mechanical engineering</t>
+          <t>Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3496,12 +3500,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440782</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441152</t>
         </is>
       </c>
     </row>
@@ -3513,37 +3517,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>3 June 2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>20 Jun 2026 - 22:00 (UTC)</t>
+          <t>5 Jul 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>University of Groningen via AcademicTransfer</t>
+          <t>Ruhr University Bochum</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PhD position Neuromorphic sensing &amp; control for bionic lower limbs</t>
+          <t>Three-year Postdoc (m/f/d) in X-ray photoemission spectroscopy of lithium batteries (TV-L 13 100%)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Computer science » Cybernetics Computer science » Programming Engineering » Biomedical engineering Engineering » Electrical engineering</t>
+          <t>Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>First Stage Researcher (R1) Recognised Researcher (R2) Established Researcher (R3) Leading Researcher (R4)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3553,12 +3557,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440781</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442179</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3574,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>3 June 2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>23 Jun 2026 - 12:00 (UTC)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3585,19 +3589,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Talentech</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Doctoral student in Interpretable and Experience-Driven Learning for Collaborative Robots</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Computer science » Programming Computer science » Other Engineering » Control engineering Engineering » Electrical engineering Engineering » Systems engineering Engineering » Other Mathematics » Applied mathematics</t>
-        </is>
-      </c>
+          <t>PhD in Plant Bioelectronics</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>First Stage Researcher (R1)</t>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440490</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441871</t>
         </is>
       </c>
     </row>
@@ -3627,37 +3627,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>3 June 2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>26 Jun 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Idiap Research Institute</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Postdoc in Trustworthy DevOps for autonomous vehicles</t>
+          <t>Postdoctoral Researcher: Trustworthy &amp; Privacy-Preserving Identity Technologies F/M</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Systems engineering Engineering » Other</t>
+          <t>Computer science</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Automotive Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440482</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442142</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>3 June 2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3704,17 +3704,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Postdoctoral studies in in molecular signature of vascular cognitive impairment and dementia (scholarship)</t>
+          <t>Assistant Professor in Data-Driven Cardiovascular Medicine</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Medical sciences</t>
+          <t>Medical sciences » Medicine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440390</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441909</t>
         </is>
       </c>
     </row>
@@ -3741,37 +3741,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>3 June 2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 23:00 (UTC)</t>
+          <t>2 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>jobRxiv</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Postdoc - Lab Automation and Data-Driven Colloid Science</t>
+          <t>Assistant Professor In Formal Methods and Neuro-Symbolic AI</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Computer science » Autonomic computing Computer science » Cybernetics</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440399</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441881</t>
         </is>
       </c>
     </row>
@@ -3798,37 +3798,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>24 Aug 2026 - 21:59 (UTC)</t>
+          <t>21 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doctoral position in landscape ecology and geospatial analysis</t>
+          <t>Postdoc Recycling of Lithium Iron Phosphate Batteries</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Environmental science » Earth science Environmental science » Ecology Environmental science » Other Geography » Human geography Geography » Other</t>
+          <t>Engineering » Chemical engineering Engineering » Process engineering</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440484</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440768</t>
         </is>
       </c>
     </row>
@@ -3855,32 +3855,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>24 Aug 2026 - 21:59 (UTC)</t>
+          <t>20 Jun 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Groningen via AcademicTransfer</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doctoral position in social indicator development with text-based and spatial data</t>
+          <t>PhD position Sensors for Neuromorphic Touch in Adaptive Robotic Grasping</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Architecture » Other Environmental science » Earth science Geography » Human geography Sociology » Urban sociology Sociology » Other</t>
+          <t>Engineering » Electrical engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440485</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440782</t>
         </is>
       </c>
     </row>
@@ -3912,32 +3912,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>28 January 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>26 Jun 2026 - 21:59 (UTC)</t>
+          <t>20 Jun 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Groningen via AcademicTransfer</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doctoral Researcher in Food Processing for Planetary and Human Health</t>
+          <t>PhD position Neuromorphic sensing &amp; control for bionic lower limbs</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Other Engineering » Other Technology » Biotechnology</t>
+          <t>Computer science » Cybernetics Computer science » Programming Engineering » Biomedical engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/404614</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440781</t>
         </is>
       </c>
     </row>
@@ -3969,32 +3969,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>23 Jun 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RWTH Aachen University</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Research Assistant/Associate (f/m/d) - V000011054</t>
+          <t>Doctoral student in Interpretable and Experience-Driven Learning for Collaborative Robots</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Computer science » Programming Computer science » Other Engineering » Control engineering Engineering » Electrical engineering Engineering » Systems engineering Engineering » Other Mathematics » Applied mathematics</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/439798</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440490</t>
         </is>
       </c>
     </row>
@@ -4026,37 +4026,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 21:59 (UTC)</t>
+          <t>26 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PhD Position Systemic Risk in Climate-Sensitive Housing Markets</t>
+          <t>Postdoc in Trustworthy DevOps for autonomous vehicles</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Environmental science » Global change Environmental science » Natural resources management</t>
+          <t>Engineering » Control engineering Engineering » Systems engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Automotive Control</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/439739</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440482</t>
         </is>
       </c>
     </row>
@@ -4083,12 +4083,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26 April 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>24 Jun 2026 - 21:59 (UTC)</t>
+          <t>8 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4098,17 +4098,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Karolinska Institutet via Varbi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Postdoc in Cognitive Science (3 years)</t>
+          <t>Postdoctoral studies in in molecular signature of vascular cognitive impairment and dementia (scholarship)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neurosciences » Neuropsychology Psychological sciences » Cognitive science Psychological sciences » Psychology</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/431660</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440390</t>
         </is>
       </c>
     </row>
@@ -4140,37 +4140,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>24 September 2025</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 23:59 (Europe/Amsterdam)</t>
+          <t>21 Jun 2026 - 23:00 (UTC)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fraunhofer ICT</t>
+          <t>jobRxiv</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PhD Position: Electrodes for hydrogen-iron flow batteries</t>
+          <t>Postdoc - Lab Automation and Data-Driven Colloid Science</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Engineering » Chemical engineering</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/375876</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440399</t>
         </is>
       </c>
     </row>
@@ -4197,37 +4197,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 21:59 (UTC)</t>
+          <t>24 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Assistant Professor in Predictive Modelling and Simulation of Rotorcraft and VTOL Aircraft</t>
+          <t>Doctoral position in landscape ecology and geospatial analysis</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Engineering » Aerospace engineering Engineering » Simulation engineering</t>
+          <t>Environmental science » Earth science Environmental science » Ecology Environmental science » Other Geography » Human geography Geography » Other</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/439041</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440484</t>
         </is>
       </c>
     </row>
@@ -4254,17 +4254,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>24 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PhD-position: Biominerals, Crystals and Climate</t>
+          <t>Doctoral position in social indicator development with text-based and spatial data</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Biological sciences » Other Chemistry » Analytical chemistry Chemistry » Biochemistry Chemistry » Inorganic chemistry Chemistry » Other Environmental science » Earth science</t>
+          <t>Architecture » Other Environmental science » Earth science Geography » Human geography Sociology » Urban sociology Sociology » Other</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/439148</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440485</t>
         </is>
       </c>
     </row>
@@ -4311,37 +4311,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>23 January 2026</t>
+          <t>28 January 2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>21 Jul 2026 - 06:04 (UTC)</t>
+          <t>26 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Postdoc on Stable Optical Circuits for Quantum Technology</t>
+          <t>Doctoral Researcher in Food Processing for Planetary and Human Health</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Physics » Optics Physics » Quantum mechanics</t>
+          <t>Agricultural sciences » Other Engineering » Other Technology » Biotechnology</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/403411</t>
+          <t>https://euraxess.ec.europa.eu/jobs/404614</t>
         </is>
       </c>
     </row>
@@ -4368,37 +4368,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>23 April 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>21 Jul 2026 - 21:59 (UTC)</t>
+          <t>23 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>RWTH Aachen University</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Postdoc position in light multiplexed, fiber-based artificial sensorimotor network</t>
+          <t>Research Assistant/Associate (f/m/d) - V000011054</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Engineering » Mechanical engineering Engineering » Other Physics » Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/430919</t>
+          <t>https://euraxess.ec.europa.eu/jobs/439798</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>22 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PhD Position Unconventional Phased Array Topologies</t>
+          <t>PhD Position Systemic Risk in Climate-Sensitive Housing Markets</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Engineering » Communication engineering Engineering » Electrical engineering</t>
+          <t>Environmental science » Global change Environmental science » Natural resources management</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438640</t>
+          <t>https://euraxess.ec.europa.eu/jobs/439739</t>
         </is>
       </c>
     </row>
@@ -4482,37 +4482,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>26 April 2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>24 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PhD Position Multi-Band Fusion in JCAS</t>
+          <t>Postdoc in Cognitive Science (3 years)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Engineering » Communication engineering Engineering » Electrical engineering</t>
+          <t>Neurosciences » Neuropsychology Psychological sciences » Cognitive science Psychological sciences » Psychology</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438641</t>
+          <t>https://euraxess.ec.europa.eu/jobs/431660</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4539,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>24 September 2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>17 Nov 2026 - 15:54 (UTC)</t>
+          <t>22 Jun 2026 - 23:59 (Europe/Amsterdam)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4554,17 +4554,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Fraunhofer ICT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PhD: Lensless 3D optical imaging</t>
+          <t>PhD Position: Electrodes for hydrogen-iron flow batteries</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Engineering » Microengineering Physics » Applied physics Physics » Optics</t>
+          <t>Engineering » Chemical engineering</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438633</t>
+          <t>https://euraxess.ec.europa.eu/jobs/375876</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22 January 2026</t>
+          <t>23 May 2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>17 Jul 2026 - 21:59 (UTC)</t>
+          <t>21 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PhD Diagnostics for interconnected complex dynamical systems</t>
+          <t>Assistant Professor in Predictive Modelling and Simulation of Rotorcraft and VTOL Aircraft</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering</t>
+          <t>Engineering » Aerospace engineering Engineering » Simulation engineering</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/403002</t>
+          <t>https://euraxess.ec.europa.eu/jobs/439041</t>
         </is>
       </c>
     </row>
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>23 May 2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4668,22 +4668,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Postdoc in Integrated Single-Photon Avalanche Diode Array for Quantum Computing</t>
+          <t>PhD-position: Biominerals, Crystals and Climate</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Electronic engineering Physics » Optics Physics » Quantum mechanics</t>
+          <t>Biological sciences » Other Chemistry » Analytical chemistry Chemistry » Biochemistry Chemistry » Inorganic chemistry Chemistry » Other Environmental science » Earth science</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438297</t>
+          <t>https://euraxess.ec.europa.eu/jobs/439148</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>23 January 2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>15 Nov 2026 - 20:33 (UTC)</t>
+          <t>21 Jul 2026 - 06:04 (UTC)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4725,22 +4725,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PhD - student: Machine learning for semiconductor wafer metrology</t>
+          <t>Postdoc on Stable Optical Circuits for Quantum Technology</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Engineering » Electronic engineering Engineering » Precision engineering</t>
+          <t>Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438306</t>
+          <t>https://euraxess.ec.europa.eu/jobs/403411</t>
         </is>
       </c>
     </row>
@@ -4767,37 +4767,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>23 April 2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>19 Jul 2026 - 21:59 (UTC)</t>
+          <t>21 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PhD in Physical control of a soft artificial heart</t>
+          <t>Postdoc position in light multiplexed, fiber-based artificial sensorimotor network</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering Engineering » Control engineering</t>
+          <t>Engineering » Mechanical engineering Engineering » Other Physics » Other</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438298</t>
+          <t>https://euraxess.ec.europa.eu/jobs/430919</t>
         </is>
       </c>
     </row>
@@ -4824,32 +4824,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>17 Aug 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PhD Students in Circular Economy and Climate Change Resilience</t>
+          <t>PhD Position Unconventional Phased Array Topologies</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Other Economics » Environmental economics Economics » Industrial economics Economics » Other Environmental science » Other Political sciences » Public policy</t>
+          <t>Engineering » Communication engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438019</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438640</t>
         </is>
       </c>
     </row>
@@ -4881,12 +4881,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20 February 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>18 Aug 2026 - 11:01 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Reconstructing nanophotonic scattering geometries from their radiation pattern</t>
+          <t>PhD Position Multi-Band Fusion in JCAS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Physics » Metrology Physics » Optics</t>
+          <t>Engineering » Communication engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/411838</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438641</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>13 Jul 2026 - 21:59 (UTC)</t>
+          <t>17 Nov 2026 - 15:54 (UTC)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4953,17 +4953,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PhD Position Safe GPAI Planning, Decision-Making and Active Perception for Reliable Robot Autonomy</t>
+          <t>PhD: Lensless 3D optical imaging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Mechanical engineering</t>
+          <t>Engineering » Microengineering Physics » Applied physics Physics » Optics</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441539</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438633</t>
         </is>
       </c>
     </row>
@@ -4995,12 +4995,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>22 January 2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>13 Jul 2026 - 21:59 (UTC)</t>
+          <t>17 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5010,17 +5010,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PhD Position Long-Term Reasoning and Adaptive Learning for Human-Aware Robot Autonomy</t>
+          <t>PhD Diagnostics for interconnected complex dynamical systems</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Engineering » Computer engineering Engineering » Control engineering</t>
+          <t>Engineering » Control engineering</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441540</t>
+          <t>https://euraxess.ec.europa.eu/jobs/403002</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>21 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5067,17 +5067,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Postdoc Spin Transport in Mesoscopic Devices with Quantum Materials</t>
+          <t>Postdoc in Integrated Single-Photon Avalanche Diode Array for Quantum Computing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
+          <t>Engineering » Electrical engineering Engineering » Electronic engineering Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441544</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438297</t>
         </is>
       </c>
     </row>
@@ -5109,32 +5109,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 12:00 (UTC)</t>
+          <t>15 Nov 2026 - 20:33 (UTC)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Talentech</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PhD students in sensor fusion and optimal motion planning for drone swarms</t>
+          <t>PhD - student: Machine learning for semiconductor wafer metrology</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Computer science » Informatics Engineering » Electronic engineering Engineering » Precision engineering</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441533</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438306</t>
         </is>
       </c>
     </row>
@@ -5166,37 +5166,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1 Aug 2026 - 21:59 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Karolinska Institutet via Varbi</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in AI Modeling of Cellular Dynamics, Alpha Cell Program</t>
+          <t>PhD in Physical control of a soft artificial heart</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neurosciences</t>
+          <t>Engineering » Biomedical engineering Engineering » Control engineering</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441545</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438298</t>
         </is>
       </c>
     </row>
@@ -5223,32 +5223,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1 Sep 2026 - 21:59 (UTC)</t>
+          <t>17 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PhD: AI-assisted discovery of chiral perovskites in nanophotonic environments</t>
+          <t>PhD Students in Circular Economy and Climate Change Resilience</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Physics » Condensed matter properties Physics » Optics</t>
+          <t>Agricultural sciences » Other Economics » Environmental economics Economics » Industrial economics Economics » Other Environmental science » Other Political sciences » Public policy</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441536</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438019</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>20 February 2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>12 Sep 2026 - 22:00 (UTC)</t>
+          <t>18 Aug 2026 - 11:01 (UTC)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5295,17 +5295,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>University of Groningen via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PhD position in Moral Philosophy, Conceptual Engineering, and Ethics of Emerging Technologies</t>
+          <t>Reconstructing nanophotonic scattering geometries from their radiation pattern</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Philosophy » Ethics</t>
+          <t>Physics » Metrology Physics » Optics</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441542</t>
+          <t>https://euraxess.ec.europa.eu/jobs/411838</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>13 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PhD Position on Life Cycle Assessment for Design of Structures</t>
+          <t>PhD Position Safe GPAI Planning, Decision-Making and Active Perception for Reliable Robot Autonomy</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Engineering » Aerospace engineering Engineering » Mechanical engineering</t>
+          <t>Engineering » Control engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/437441</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441539</t>
         </is>
       </c>
     </row>
@@ -5394,32 +5394,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>13 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doctoral student in thermal packaging solutions for future communication and sensor systems</t>
+          <t>PhD Position Long-Term Reasoning and Adaptive Learning for Human-Aware Robot Autonomy</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Engineering » Communication engineering Engineering » Electrical engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Other Physics » Electromagnetism Physics » Thermodynamics</t>
+          <t>Engineering » Computer engineering Engineering » Control engineering</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446320</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441540</t>
         </is>
       </c>
     </row>
@@ -5451,37 +5451,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>30 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doctoral student in machine-learning for exploration of sustainable welding materials</t>
+          <t>Postdoc Spin Transport in Mesoscopic Devices with Quantum Materials</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chemistry » Computational chemistry Chemistry » Physical chemistry Chemistry » Other Computer science » Other Engineering » Chemical engineering Engineering » Materials engineering Physics » Thermodynamics Physics » Other Technology » Energy technology</t>
+          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446323</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441544</t>
         </is>
       </c>
     </row>
@@ -5508,37 +5508,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>13 Jul 2026 - 21:59 (UTC)</t>
+          <t>22 Jun 2026 - 12:00 (UTC)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Talentech</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Postdoctoral fellow opening: Ambulatory Biomechanics, Sensor Fusion, and Machine Learning for Wearable Robotics</t>
+          <t>PhD students in sensor fusion and optimal motion planning for drone swarms</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering Engineering » Control engineering</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446245</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441533</t>
         </is>
       </c>
     </row>
@@ -5565,12 +5565,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 21:59 (UTC)</t>
+          <t>1 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Karolinska Institutet via Varbi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Postdoctoral position in Biomedical Engineering with a focus on neuroengineering</t>
+          <t>Postdoctoral Researcher in AI Modeling of Cellular Dynamics, Alpha Cell Program</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering</t>
+          <t>Neurosciences</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446297</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441545</t>
         </is>
       </c>
     </row>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 21:59 (UTC)</t>
+          <t>1 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PhD in Credible hybrid AI-mechanistic models for clinical decision-making: unveiling the untapped potential of sensitivity a...</t>
+          <t>PhD: AI-assisted discovery of chiral perovskites in nanophotonic environments</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering Mathematics » Applied mathematics Medical sciences » Medicine</t>
+          <t>Physics » Condensed matter properties Physics » Optics</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446243</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441536</t>
         </is>
       </c>
     </row>
@@ -5679,37 +5679,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>17 Jul 2026 - 21:59 (UTC)</t>
+          <t>12 Sep 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Groningen via AcademicTransfer</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Postdoc in AI-Driven Materials Discovery</t>
+          <t>PhD position in Moral Philosophy, Conceptual Engineering, and Ethics of Emerging Technologies</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chemistry » Computational chemistry Computer science » Other Engineering » Materials engineering Engineering » Other Physics » Chemical physics Physics » Computational physics Physics » Other</t>
+          <t>Philosophy » Ethics</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446319</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441542</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5751,22 +5751,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PhD Candidate in Agent-Based Modelling and Urban Health: Designing for Movement</t>
+          <t>PhD Position on Life Cycle Assessment for Design of Structures</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Engineering » Simulation engineering Environmental science » Global change Geography » Human geography Geography » Social geography</t>
+          <t>Engineering » Aerospace engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) First Stage Researcher (R1)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446247</t>
+          <t>https://euraxess.ec.europa.eu/jobs/437441</t>
         </is>
       </c>
     </row>
@@ -5798,32 +5798,32 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>16 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PhD position VIDI project With greater power must come great responsibility</t>
+          <t>Doctoral student in thermal packaging solutions for future communication and sensor systems</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Juridical sciences » European law Juridical sciences » Informatic law</t>
+          <t>Engineering » Communication engineering Engineering » Electrical engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Other Physics » Electromagnetism Physics » Thermodynamics</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) First Stage Researcher (R1)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446250</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446320</t>
         </is>
       </c>
     </row>
@@ -5855,32 +5855,32 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>14 Jul 2026 - 22:00 (UTC)</t>
+          <t>30 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Staff scientist (f/m/x) Core Facility Bioinformatics and Statistics</t>
+          <t>Doctoral student in machine-learning for exploration of sustainable welding materials</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Medical sciences</t>
+          <t>Chemistry » Computational chemistry Chemistry » Physical chemistry Chemistry » Other Computer science » Other Engineering » Chemical engineering Engineering » Materials engineering Physics » Thermodynamics Physics » Other Technology » Energy technology</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446270</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446323</t>
         </is>
       </c>
     </row>
@@ -5912,32 +5912,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>22 Jul 2026 - 21:59 (UTC)</t>
+          <t>13 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Doctoral student in Physics with a focus on the development of novel X-ray imaging methods with beam-steering ptychography and AI</t>
+          <t>Postdoctoral fellow opening: Ambulatory Biomechanics, Sensor Fusion, and Machine Learning for Wearable Robotics</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Engineering » Biomedical engineering Engineering » Control engineering</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446295</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446245</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5984,17 +5984,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Doctoral student in Physics; Nanoscale X-ray diffraction for ferroelectric domain dynamics</t>
+          <t>Postdoctoral position in Biomedical Engineering with a focus on neuroengineering</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Engineering » Biomedical engineering</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446296</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446297</t>
         </is>
       </c>
     </row>
@@ -6021,37 +6021,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Postdoc in Coupled transport-energy modeling with focus on transport systems</t>
+          <t>PhD in Credible hybrid AI-mechanistic models for clinical decision-making: unveiling the untapped potential of sensitivity a...</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Engineering » Systems engineering Engineering » Other Technology » Energy technology Technology » Transport technology</t>
+          <t>Engineering » Biomedical engineering Mathematics » Applied mathematics Medical sciences » Medicine</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445879</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446243</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>15 Sep 2026 - 21:59 (UTC)</t>
+          <t>17 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6098,12 +6098,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Postdoc position in AI and Machine Learning for Electromobility</t>
+          <t>Postdoc in AI-Driven Materials Discovery</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Mathematics » Applied mathematics Technology » Energy technology</t>
+          <t>Chemistry » Computational chemistry Computer science » Other Engineering » Materials engineering Engineering » Other Physics » Chemical physics Physics » Computational physics Physics » Other</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445866</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446319</t>
         </is>
       </c>
     </row>
@@ -6135,37 +6135,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>15 Sep 2026 - 21:59 (UTC)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PhD position in Computational earthquake rupture mechanics</t>
+          <t>PhD Candidate in Agent-Based Modelling and Urban Health: Designing for Movement</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Engineering » Other Environmental science » Earth science Mathematics » Applied mathematics Physics » Applied physics Physics » Computational physics Physics » Other</t>
+          <t>Engineering » Simulation engineering Environmental science » Global change Geography » Human geography Geography » Social geography</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445872</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446247</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>29 Jul 2026 - 21:59 (UTC)</t>
+          <t>16 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6207,22 +6207,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Post-Doctoral Researcher in Computational Geomechanics of Gas Migration in Clays</t>
+          <t>PhD position VIDI project With greater power must come great responsibility</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Engineering » Civil engineering Engineering » Geological engineering Geosciences » Geology Geosciences » Hydrology</t>
+          <t>Juridical sciences » European law Juridical sciences » Informatic law</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445750</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446250</t>
         </is>
       </c>
     </row>
@@ -6249,37 +6249,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>14 Jul 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Postdoc Position in Cloud and Edge Systems</t>
+          <t>Staff scientist (f/m/x) Core Facility Bioinformatics and Statistics</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Computer science » Computer systems Computer science » Programming Engineering » Computer engineering Engineering » Systems engineering</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445749</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446270</t>
         </is>
       </c>
     </row>
@@ -6306,32 +6306,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>22 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PhD Universal mechanobiological gateways to Cardiac Regeneration across regenerative and non-regenerative species</t>
+          <t>Doctoral student in Physics with a focus on the development of novel X-ray imaging methods with beam-steering ptychography and AI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445754</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446295</t>
         </is>
       </c>
     </row>
@@ -6363,12 +6363,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>21 Aug 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6378,17 +6378,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Umeå Stipendier</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Postdoctoral scholarship (2 years) in mid-infrared photothermal microscopy</t>
+          <t>Doctoral student in Physics; Nanoscale X-ray diffraction for ferroelectric domain dynamics</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Physics » Applied physics</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445809</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446296</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>21 Aug 2026 - 12:00 (UTC)</t>
+          <t>8 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6435,22 +6435,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Talentech</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PhD student in generative modeling for data-efficient machine learning</t>
+          <t>Postdoc in Coupled transport-energy modeling with focus on transport systems</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Computer science</t>
+          <t>Computer science » Other Engineering » Electrical engineering Engineering » Systems engineering Engineering » Other Technology » Energy technology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445739</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445879</t>
         </is>
       </c>
     </row>
@@ -6477,37 +6477,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>23 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Maastricht University via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>PhD Candidate in Mass Spectrometry Instrumentation</t>
+          <t>Postdoc position in AI and Machine Learning for Electromobility</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Computer science » Other Engineering » Electrical engineering Mathematics » Applied mathematics Technology » Energy technology</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445398</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445866</t>
         </is>
       </c>
     </row>
@@ -6534,37 +6534,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>14 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Postdoc - Design of Experiment and Digital Process Optimization for CO2 Electrolysis</t>
+          <t>PhD position in Computational earthquake rupture mechanics</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Engineering » Other Environmental science » Earth science Mathematics » Applied mathematics Physics » Applied physics Physics » Computational physics Physics » Other</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445415</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445872</t>
         </is>
       </c>
     </row>
@@ -6591,12 +6591,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>19 Jul 2026 - 21:59 (UTC)</t>
+          <t>29 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6611,17 +6611,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>PhD Position in Extended Reality for Safe and Active Mobility</t>
+          <t>Post-Doctoral Researcher in Computational Geomechanics of Gas Migration in Clays</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Engineering » Civil engineering Engineering » Computer engineering</t>
+          <t>Engineering » Civil engineering Engineering » Geological engineering Geosciences » Geology Geosciences » Hydrology</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445389</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445750</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>19 Jul 2026 - 21:59 (UTC)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>PhD Position in Data and AI for Multi-Source Micromobility Safety Analytics</t>
+          <t>Postdoc Position in Cloud and Edge Systems</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Engineering » Civil engineering Engineering » Computer engineering</t>
+          <t>Computer science » Computer systems Computer science » Programming Engineering » Computer engineering Engineering » Systems engineering</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445390</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445749</t>
         </is>
       </c>
     </row>
@@ -6705,32 +6705,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>17 Aug 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Uppsala Universitet via MyNetwork</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Doctoral (Phd) position in Tribology with focus on Sustainable transformer oils for electrical contacts</t>
+          <t>PhD Universal mechanobiological gateways to Cardiac Regeneration across regenerative and non-regenerative species</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering</t>
+          <t>Engineering » Biomedical engineering</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6745,12 +6745,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445381</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445754</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>9 Aug 2026 - 21:59 (UTC)</t>
+          <t>21 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6777,22 +6777,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Jönköpings University</t>
+          <t>Umeå Stipendier</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Assistant Professor or Senior Associate Lecturer with a focus on Automation</t>
+          <t>Postdoctoral scholarship (2 years) in mid-infrared photothermal microscopy</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Physics » Applied physics</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Virtual Sensor</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445379</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445809</t>
         </is>
       </c>
     </row>
@@ -6819,32 +6819,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1 Aug 2026 - 17:00 (Europe/Zurich)</t>
+          <t>21 Aug 2026 - 12:00 (UTC)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>HES-SO Genève</t>
+          <t>Talentech</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>PhD position in applied research - Dynamic risk assessment for Critical Infrastructure Security</t>
+          <t>PhD student in generative modeling for data-efficient machine learning</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Computer science » Other</t>
+          <t>Computer science</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445626</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445739</t>
         </is>
       </c>
     </row>
@@ -6881,27 +6881,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>23 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Maastricht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Doctoral student in Computer Science with a focus on Human-Swarm Interaction and Adaptive Swarm Teamwork</t>
+          <t>PhD Candidate in Mass Spectrometry Instrumentation</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Other</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6916,12 +6916,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445460</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445398</t>
         </is>
       </c>
     </row>
@@ -6938,32 +6938,32 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>14 Sep 2026 - 21:59 (UTC)</t>
+          <t>14 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PhD Position in AI-Supported Resilience Assessment of Climate-Neutral Transport Infrastructure</t>
+          <t>Postdoc - Design of Experiment and Digital Process Optimization for CO2 Electrolysis</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Civil engineering Engineering » Other Environmental science » Earth science Technology » Environmental technology Technology » Transport technology</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445465</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445415</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>12 Jul 2026 - 21:59 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7005,17 +7005,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maastricht University via AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PhD Position in Neuro-Musculoskeletal Cell-Materials Atlas</t>
+          <t>PhD Position in Extended Reality for Safe and Active Mobility</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Biological sciences » Biology Engineering » Biomaterial engineering Engineering » Biomedical engineering</t>
+          <t>Engineering » Civil engineering Engineering » Computer engineering</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445385</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445389</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7067,17 +7067,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Postdoc Superconducting Single Photon Detector Arrays for Imaging</t>
+          <t>PhD Position in Data and AI for Multi-Source Micromobility Safety Analytics</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Microengineering Physics » Optics Physics » Quantum mechanics</t>
+          <t>Engineering » Civil engineering Engineering » Computer engineering</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445387</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445390</t>
         </is>
       </c>
     </row>
@@ -7109,27 +7109,27 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>17 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Uppsala Universitet via MyNetwork</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PhD Position on Thin Film Energy Materials</t>
+          <t>Doctoral (Phd) position in Tribology with focus on Sustainable transformer oils for electrical contacts</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Engineering » Chemical engineering Engineering » Materials engineering</t>
+          <t>Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445392</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445381</t>
         </is>
       </c>
     </row>
@@ -7166,32 +7166,32 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>28 Jul 2026 - 21:59 (UTC)</t>
+          <t>9 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Jönköpings University</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Postdoc Scalable Graph Learning</t>
+          <t>Assistant Professor or Senior Associate Lecturer with a focus on Automation</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Computer science » Programming</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Virtual Sensor</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445393</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445379</t>
         </is>
       </c>
     </row>
@@ -7223,32 +7223,32 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1 Aug 2026 - 21:59 (UTC)</t>
+          <t>1 Aug 2026 - 17:00 (Europe/Zurich)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Wageningen University and Research Centre via AcademicTransfer</t>
+          <t>HES-SO Genève</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lecturer in Big Data and Artificial Intelligence</t>
+          <t>PhD position in applied research - Dynamic risk assessment for Critical Infrastructure Security</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Computer science » Database management Computer science » Programming</t>
+          <t>Computer science » Other</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445395</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445626</t>
         </is>
       </c>
     </row>
@@ -7280,27 +7280,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:14 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Postdoc or PhD Candidate (f/m/x) - AI Augmented Target Discovery in Translational Kidney Disease</t>
+          <t>Doctoral student in Computer Science with a focus on Human-Swarm Interaction and Adaptive Swarm Teamwork</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Medical sciences</t>
+          <t>Computer science » Other Engineering » Other</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445411</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445460</t>
         </is>
       </c>
     </row>
@@ -7332,32 +7332,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>16 June 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>20 Jul 2026 - 21:59 (UTC)</t>
+          <t>14 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PhD in Quantum Algorithms for Chemistry</t>
+          <t>PhD Position in AI-Supported Resilience Assessment of Climate-Neutral Transport Infrastructure</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chemistry » Computational chemistry Chemistry » Physical chemistry Computer science » Informatics Computer science » Programming Physics » Computational physics Physics » Quantum mechanics</t>
+          <t>Computer science » Other Engineering » Civil engineering Engineering » Other Environmental science » Earth science Technology » Environmental technology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445028</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445465</t>
         </is>
       </c>
     </row>
@@ -7389,12 +7389,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16 June 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>18 Aug 2026 - 21:59 (UTC)</t>
+          <t>12 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7404,22 +7404,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Maastricht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>EngD in Data Interaction for Remote Heart Failure Monitoring</t>
+          <t>PhD Position in Neuro-Musculoskeletal Cell-Materials Atlas</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Computer science » Systems design Engineering » Biomedical engineering Engineering » Systems engineering</t>
+          <t>Biological sciences » Biology Engineering » Biomaterial engineering Engineering » Biomedical engineering</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445023</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445385</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>16 June 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7461,17 +7461,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Erasmus University Rotterdam via AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher - EU Horizon Projects</t>
+          <t>Postdoc Superconducting Single Photon Detector Arrays for Imaging</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Communication sciences » Media studies Sociology » Social shaping of technology Sociology » Sociology of labour</t>
+          <t>Engineering » Electrical engineering Engineering » Microengineering Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445026</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445387</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7503,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>16 June 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>15 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PhD Position Microclimate Adaptive Grid CFD Modeling</t>
+          <t>PhD Position on Thin Film Energy Materials</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Agronomics Agricultural sciences » Phytotechny Engineering » Civil engineering Engineering » Mechanical engineering</t>
+          <t>Engineering » Chemical engineering Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445031</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445392</t>
         </is>
       </c>
     </row>
@@ -7560,12 +7560,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>15 Aug 2026 - 21:59 (UTC)</t>
+          <t>28 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7575,22 +7575,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Assistant Professors in Mission-Driven Research on Future-Proof Networks</t>
+          <t>Postdoc Scalable Graph Learning</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Mathematics » Discrete mathematics Mathematics » Probability theory Mathematics » Statistics</t>
+          <t>Computer science » Informatics Computer science » Programming</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/436378</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445393</t>
         </is>
       </c>
     </row>
@@ -7617,37 +7617,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>14 June 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Wageningen University and Research Centre via AcademicTransfer</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Doctoral student in Physics within AI-accelerated AlN MOCVD growth</t>
+          <t>Lecturer in Big Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Computer science » Database management Computer science » Programming</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444805</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445395</t>
         </is>
       </c>
     </row>
@@ -7674,37 +7674,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>14 June 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>12 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:14 (UTC)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wageningen University and Research Centre via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Researcher in Fish Physiology</t>
+          <t>Postdoc or PhD Candidate (f/m/x) - AI Augmented Target Discovery in Translational Kidney Disease</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Zootechnics Biological sciences » Nutritional sciences Biological sciences » Zoology</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444799</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445411</t>
         </is>
       </c>
     </row>
@@ -7731,37 +7731,37 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>16 June 2026</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>18 Jul 2026 - 22:00 (UTC)</t>
+          <t>20 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ABG  - Association Bernard Gregory</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>NCCR Clim+: PhD Water and Agriculture</t>
+          <t>PhD in Quantum Algorithms for Chemistry</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Environmental science » Ecology Agricultural sciences » Agronomics Geography</t>
+          <t>Chemistry » Computational chemistry Chemistry » Physical chemistry Computer science » Informatics Computer science » Programming Physics » Computational physics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Leading Researcher (R4) First Stage Researcher (R1) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/435811</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445028</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>16 June 2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>9 Jul 2026 - 21:59 (UTC)</t>
+          <t>18 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7803,17 +7803,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>(Junior) Researcher</t>
+          <t>EngD in Data Interaction for Remote Heart Failure Monitoring</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Engineering » Biomaterial engineering Engineering » Materials engineering</t>
+          <t>Computer science » Informatics Computer science » Systems design Engineering » Biomedical engineering Engineering » Systems engineering</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444640</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445023</t>
         </is>
       </c>
     </row>
@@ -7845,12 +7845,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>16 June 2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>28 Jun 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7860,22 +7860,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Erasmus University Rotterdam via AcademicTransfer</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Junior lecturer in Energy Sciences</t>
+          <t>Postdoctoral Researcher - EU Horizon Projects</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Engineering » Thermal engineering Environmental science » Global change Environmental science » Natural resources management</t>
+          <t>Communication sciences » Media studies Sociology » Social shaping of technology Sociology » Sociology of labour</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444653</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445026</t>
         </is>
       </c>
     </row>
@@ -7902,32 +7902,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>16 June 2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>15 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PhD Position - Control System for the Climate-Neutral Operation of the Einstein Telescope's Computing Centre</t>
+          <t>PhD Position Microclimate Adaptive Grid CFD Modeling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Agricultural sciences » Agronomics Agricultural sciences » Phytotechny Engineering » Civil engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444669</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445031</t>
         </is>
       </c>
     </row>
@@ -7959,37 +7959,37 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>10 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PhD on Hydrological model-data interaction and machine learning for headwater catchment analyses</t>
+          <t>Assistant Professors in Mission-Driven Research on Future-Proof Networks</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Computer science » Other Environmental science » Earth science Environmental science » Other</t>
+          <t>Mathematics » Discrete mathematics Mathematics » Probability theory Mathematics » Statistics</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444752</t>
+          <t>https://euraxess.ec.europa.eu/jobs/436378</t>
         </is>
       </c>
     </row>
@@ -8016,32 +8016,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>14 June 2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PhD Position Structural Biology of the Neuronal Synapse</t>
+          <t>Doctoral student in Physics within AI-accelerated AlN MOCVD growth</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neurosciences » Neurobiology Neurosciences » Neurochemistry</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444634</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444805</t>
         </is>
       </c>
     </row>
@@ -8073,37 +8073,37 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>14 June 2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>12 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Wageningen University and Research Centre via AcademicTransfer</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PhD Position - Generative AI for Smart Grids and Energy Systems</t>
+          <t>Researcher in Fish Physiology</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Agricultural sciences » Zootechnics Biological sciences » Nutritional sciences Biological sciences » Zoology</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444670</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444799</t>
         </is>
       </c>
     </row>
@@ -8130,37 +8130,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>16 Aug 2026 - 21:59 (UTC)</t>
+          <t>18 Jul 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>ABG  - Association Bernard Gregory</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Doctoral student in statistical shape modelling of the human body for vehicle safety applications</t>
+          <t>NCCR Clim+: PhD Water and Agriculture</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other Mathematics » Statistics Medical sciences » Other Physics » Other</t>
+          <t>Environmental science » Ecology Agricultural sciences » Agronomics Geography</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Leading Researcher (R4) First Stage Researcher (R1) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444767</t>
+          <t>https://euraxess.ec.europa.eu/jobs/435811</t>
         </is>
       </c>
     </row>
@@ -8192,27 +8192,27 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>9 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Postdoc in Trustworthy AI for Localization and Sensing</t>
+          <t>(Junior) Researcher</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Communication engineering Engineering » Other Mathematics » Probability theory Mathematics » Statistics</t>
+          <t>Engineering » Biomaterial engineering Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444768</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444640</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>11 Jul 2026 - 21:59 (UTC)</t>
+          <t>28 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8259,22 +8259,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PhD in Process-Aware AI Agents for Autonomous Manufacturing at Process Analytics Cluster</t>
+          <t>Junior lecturer in Energy Sciences</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Computer science » Programming Engineering » Industrial engineering Engineering » Process engineering</t>
+          <t>Engineering » Thermal engineering Environmental science » Global change Environmental science » Natural resources management</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444646</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444653</t>
         </is>
       </c>
     </row>
@@ -8306,32 +8306,32 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>12 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Post-doctoral fellow in Physics; fast time-resolved 3D imaging with X-ray multi-projection imaging for advanced manufacturing</t>
+          <t>PhD Position - Control System for the Climate-Neutral Operation of the Einstein Telescope's Computing Centre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444730</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444669</t>
         </is>
       </c>
     </row>
@@ -8363,27 +8363,27 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>11 Jul 2026 - 21:59 (UTC)</t>
+          <t>10 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>PhD in Active Inference for Manufacturing Processes</t>
+          <t>PhD on Hydrological model-data interaction and machine learning for headwater catchment analyses</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Industrial engineering</t>
+          <t>Computer science » Other Environmental science » Earth science Environmental science » Other</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444648</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444752</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>11 Jul 2026 - 21:59 (UTC)</t>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8430,17 +8430,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>PhD in AI for reconfigurable robot collectives and real-time flow control</t>
+          <t>PhD Position Structural Biology of the Neuronal Synapse</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Computer science » Cybernetics Computer science » Programming Engineering » Control engineering Engineering » Mechanical engineering</t>
+          <t>Neurosciences » Neurobiology Neurosciences » Neurochemistry</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444649</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444634</t>
         </is>
       </c>
     </row>
@@ -8477,27 +8477,27 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>13 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Doctoral Student in Human-in-the-Loop Autonomous Systems</t>
+          <t>PhD Position - Generative AI for Smart Grids and Energy Systems</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other Engineering » Control engineering Engineering » Other</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444766</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444670</t>
         </is>
       </c>
     </row>
@@ -8534,27 +8534,27 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>15 Sep 2026 - 21:59 (UTC)</t>
+          <t>16 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Three fully funded PhD positions in Competition Law and AI</t>
+          <t>Doctoral student in statistical shape modelling of the human body for vehicle safety applications</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Juridical sciences » European law Juridical sciences » Informatic law</t>
+          <t>Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other Mathematics » Statistics Medical sciences » Other Physics » Other</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444655</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444767</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8601,22 +8601,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Doctoral student in Biophysical Chemistry and Protein Self-Assembly</t>
+          <t>Postdoc in Trustworthy AI for Localization and Sensing</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Computer science » Other Engineering » Communication engineering Engineering » Other Mathematics » Probability theory Mathematics » Statistics</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444731</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444768</t>
         </is>
       </c>
     </row>
@@ -8648,27 +8648,27 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 21:59 (UTC)</t>
+          <t>11 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Research Engineer in Machine Learning and Health Data</t>
+          <t>PhD in Process-Aware AI Agents for Autonomous Manufacturing at Process Analytics Cluster</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other</t>
+          <t>Computer science » Informatics Computer science » Programming Engineering » Industrial engineering Engineering » Process engineering</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444755</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444646</t>
         </is>
       </c>
     </row>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>12 June 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>16 Aug 2026 - 21:59 (UTC)</t>
+          <t>12 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8715,17 +8715,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Postdoc in Sodium-ion batteries for transport: from materials to cell performance</t>
+          <t>Post-doctoral fellow in Physics; fast time-resolved 3D imaging with X-ray multi-projection imaging for advanced manufacturing</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chemistry » Other Engineering » Chemical engineering Engineering » Electrical engineering Engineering » Materials engineering Engineering » Other Technology » Energy technology</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444376</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444730</t>
         </is>
       </c>
     </row>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>12 June 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>29 Jun 2026 - 21:59 (UTC)</t>
+          <t>11 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>PhD Position Socio-Economic Modelling of Nature Restoration at European scale</t>
+          <t>PhD in Active Inference for Manufacturing Processes</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Economics » Applied economics Economics » Environmental economics Environmental science » Ecology Environmental science » Natural resources management</t>
+          <t>Engineering » Electrical engineering Engineering » Industrial engineering</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444237</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444648</t>
         </is>
       </c>
     </row>
@@ -8814,37 +8814,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>12 June 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>15 Aug 2026 - 21:59 (UTC)</t>
+          <t>11 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Postdoc in Modeling of Human-like Balance and Step Recovery</t>
+          <t>PhD in AI for reconfigurable robot collectives and real-time flow control</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other Technology » Transport technology</t>
+          <t>Computer science » Cybernetics Computer science » Programming Engineering » Control engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444375</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444649</t>
         </is>
       </c>
     </row>
@@ -8871,37 +8871,37 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>12 June 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>9 Jul 2026 - 21:59 (UTC)</t>
+          <t>13 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Postdoc Advanced Ultrasound Arrays Technology</t>
+          <t>Doctoral Student in Human-in-the-Loop Autonomous Systems</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering Engineering » Electrical engineering</t>
+          <t>Computer science » Programming Computer science » Other Engineering » Control engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444239</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444766</t>
         </is>
       </c>
     </row>
@@ -8928,12 +8928,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>12 June 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8943,22 +8943,22 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Postdoc Surface Water Salinity Intrusion in the Ganges-Brahmaputra-Meghna Delta</t>
+          <t>Three fully funded PhD positions in Competition Law and AI</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Engineering » Civil engineering Engineering » Water resources engineering Environmental science » Water science</t>
+          <t>Computer science » Informatics Juridical sciences » European law Juridical sciences » Informatic law</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444232</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444655</t>
         </is>
       </c>
     </row>
@@ -8985,37 +8985,37 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 23:59 (Europe/Berlin)</t>
+          <t>2 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Constructor University Bremen gGmbH</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Biotechnology (m/f/d)</t>
+          <t>Doctoral student in Biophysical Chemistry and Protein Self-Assembly</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Technology » Biotechnology</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/435218</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444731</t>
         </is>
       </c>
     </row>
@@ -9042,37 +9042,37 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>28 Jul 2026 - 23:59 (Europe/Berlin)</t>
+          <t>21 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Brandenburgische Technische Universität Cottbus</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>PROFESSORSHIP (W3) Aerospace Propulsion Technology (Luftfahrtantriebe)</t>
+          <t>Research Engineer in Machine Learning and Health Data</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Engineering » Other Physics » Other</t>
+          <t>Computer science » Programming Computer science » Other</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444058</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444755</t>
         </is>
       </c>
     </row>
@@ -9099,37 +9099,37 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>12 June 2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>24 Jun 2026 - 21:59 (UTC)</t>
+          <t>16 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>PhD Position Packaging Solutions</t>
+          <t>Postdoc in Sodium-ion batteries for transport: from materials to cell performance</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Engineering » Electronic engineering Engineering » Materials engineering</t>
+          <t>Chemistry » Other Engineering » Chemical engineering Engineering » Electrical engineering Engineering » Materials engineering Engineering » Other Technology » Energy technology</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443845</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444376</t>
         </is>
       </c>
     </row>
@@ -9156,32 +9156,32 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>12 June 2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 00:00 (Europe/Berlin)</t>
+          <t>29 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Leibniz Institute of Vegetable and Ornamental Crops</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>PhD student (f,m,div) in Plant Biology</t>
+          <t>PhD Position Socio-Economic Modelling of Nature Restoration at European scale</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Biological sciences » Biology</t>
+          <t>Economics » Applied economics Economics » Environmental economics Environmental science » Ecology Environmental science » Natural resources management</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444197</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444237</t>
         </is>
       </c>
     </row>
@@ -9213,17 +9213,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>12 June 2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>7 Sep 2026 - 21:59 (UTC)</t>
+          <t>15 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher - Bone Organoids</t>
+          <t>Postdoc in Modeling of Human-like Balance and Step Recovery</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Biological sciences » Other Engineering » Biomedical engineering Physics » Biophysics Technology » Biotechnology</t>
+          <t>Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other Technology » Transport technology</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443947</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444375</t>
         </is>
       </c>
     </row>
@@ -9270,37 +9270,37 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>12 June 2026</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>11 Aug 2026 - 21:59 (UTC)</t>
+          <t>9 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Doctoral student in Resilient and Equitable Mobility Systems</t>
+          <t>Postdoc Advanced Ultrasound Arrays Technology</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other Environmental science » Earth science Mathematics » Applied mathematics Sociology » Urban sociology Technology » Transport technology</t>
+          <t>Engineering » Biomedical engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443957</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444239</t>
         </is>
       </c>
     </row>
@@ -9327,32 +9327,32 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>12 June 2026</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>11 Aug 2026 - 21:59 (UTC)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Postdoc in Resilient and Equitable Mobility Systems</t>
+          <t>Postdoc Surface Water Salinity Intrusion in the Ganges-Brahmaputra-Meghna Delta</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Computer science » Other Environmental science » Earth science Geography » Other Mathematics » Applied mathematics Sociology » Urban sociology Technology » Transport technology</t>
+          <t>Engineering » Civil engineering Engineering » Water resources engineering Environmental science » Water science</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9367,12 +9367,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443958</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444232</t>
         </is>
       </c>
     </row>
@@ -9384,37 +9384,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>9 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Constructor University Bremen gGmbH</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Postdoc on human-centric, collaborative AI</t>
+          <t>Assistant / Associate Professor of Biotechnology (m/f/d)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Computer science » Cybernetics Computer science » Programming</t>
+          <t>Technology » Biotechnology</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443852</t>
+          <t>https://euraxess.ec.europa.eu/jobs/435218</t>
         </is>
       </c>
     </row>
@@ -9446,32 +9446,32 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>28 Jul 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Umeå Stipendier</t>
+          <t>Brandenburgische Technische Universität Cottbus</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Postdoctoral scholarship (2 years) within Optimization and Learning for Distributed Decision Systems</t>
+          <t>PROFESSORSHIP (W3) Aerospace Propulsion Technology (Luftfahrtantriebe)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Mathematics » Statistics</t>
+          <t>Engineering » Other Physics » Other</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443888</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444058</t>
         </is>
       </c>
     </row>
@@ -9503,32 +9503,32 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>9 Jul 2026 - 21:59 (UTC)</t>
+          <t>24 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Postdoc in Quality-Aware Machine Learning and AI Systems</t>
+          <t>PhD Position Packaging Solutions</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Computer science » Other Mathematics » Statistics</t>
+          <t>Engineering » Electronic engineering Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443955</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443845</t>
         </is>
       </c>
     </row>
@@ -9560,32 +9560,32 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>15 Jul 2026 - 21:59 (UTC)</t>
+          <t>5 Jul 2026 - 00:00 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Leibniz Institute of Vegetable and Ornamental Crops</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher for Data Analysis</t>
+          <t>PhD student (f,m,div) in Plant Biology</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Geosciences » Geology</t>
+          <t>Biological sciences » Biology</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443846</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444197</t>
         </is>
       </c>
     </row>
@@ -9617,27 +9617,27 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>24 Jul 2026 - 21:59 (UTC)</t>
+          <t>7 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Postdoc in geopolitics and governance of chip security value chains</t>
+          <t>Postdoctoral Researcher - Bone Organoids</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Geography » Geopolitics</t>
+          <t>Biological sciences » Other Engineering » Biomedical engineering Physics » Biophysics Technology » Biotechnology</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443848</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443947</t>
         </is>
       </c>
     </row>
@@ -9669,32 +9669,32 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>10 June 2026</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>11 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>PhD position in multi-material additive manufacturing for advanced chip cooling</t>
+          <t>Doctoral student in Resilient and Equitable Mobility Systems</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Thermal engineering</t>
+          <t>Computer science » Programming Computer science » Other Environmental science » Earth science Mathematics » Applied mathematics Sociology » Urban sociology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443575</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443957</t>
         </is>
       </c>
     </row>
@@ -9726,17 +9726,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>10 June 2026</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>6 Sep 2026 - 21:59 (UTC)</t>
+          <t>11 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9746,17 +9746,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>PhD position in Soft Robotics Systems</t>
+          <t>Postdoc in Resilient and Equitable Mobility Systems</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other</t>
+          <t>Computer science » Other Environmental science » Earth science Geography » Other Mathematics » Applied mathematics Sociology » Urban sociology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443648</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443958</t>
         </is>
       </c>
     </row>
@@ -9783,32 +9783,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>10 June 2026</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>29 Jun 2026 - 21:59 (UTC)</t>
+          <t>9 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Postdoctoral position in Electrical Engineering focusing on Machine Learning</t>
+          <t>Postdoc on human-centric, collaborative AI</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering</t>
+          <t>Computer science » Cybernetics Computer science » Programming</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443632</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443852</t>
         </is>
       </c>
     </row>
@@ -9840,37 +9840,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>10 June 2026</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Umeå Stipendier</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>PhD position for NWO project ECHoFAIR: empowering collaborative human-AI teaming for failure analysis and intelligent risk a...</t>
+          <t>Postdoctoral scholarship (2 years) within Optimization and Learning for Distributed Decision Systems</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Computer science » Cybernetics Computer science » Informatics Engineering » Industrial engineering Engineering » Systems engineering</t>
+          <t>Mathematics » Statistics</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443574</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443888</t>
         </is>
       </c>
     </row>
@@ -9897,50 +9897,449 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>11 June 2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>9 Jul 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Academic Positions</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Postdoc in Quality-Aware Machine Learning and AI Systems</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Computer science » Other Mathematics » Statistics</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Explainable AI</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443955</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>11 June 2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>15 Jul 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Utrecht University via AcademicTransfer</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Postdoctoral Researcher for Data Analysis</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Geosciences » Geology</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Explainable AI</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443846</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>11 June 2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>24 Jul 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Postdoc in geopolitics and governance of chip security value chains</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Geography » Geopolitics</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Explainable AI</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443848</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>10 June 2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AcademicTransfer</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>PhD position in multi-material additive manufacturing for advanced chip cooling</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Thermal engineering</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Thermal Management</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443575</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>10 June 2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>6 Sep 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Academic Positions</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>PhD position in Soft Robotics Systems</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Computer science » Other Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Climate Control</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443648</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>10 June 2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>29 Jun 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Lund University via MyNetwork</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Postdoctoral position in Electrical Engineering focusing on Machine Learning</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Engineering » Electrical engineering</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Domain Adaptation</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443632</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>10 June 2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AcademicTransfer</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>PhD position for NWO project ECHoFAIR: empowering collaborative human-AI teaming for failure analysis and intelligent risk a...</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Computer science » Cybernetics Computer science » Informatics Engineering » Industrial engineering Engineering » Systems engineering</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Explainable AI</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443574</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
           <t>1 June 2026</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>31 Jul 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>University of Bremen</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>2 independent postdoctoral researchers (f/m/d) - The Martian Mindset Open Idea Competition</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>Recognised Researcher (R2)</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
         <is>
           <t>Explainable AI</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t>https://euraxess.ec.europa.eu/jobs/441376</t>
         </is>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:K187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -495,42 +495,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21 June 2026</t>
+          <t>22 June 2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>19 Jul 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wageningen University and Research Centre via AcademicTransfer</t>
+          <t>Academic Europe</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Postdoc: Evolution of Taste Receptors in Specialist Insect–Plant Interactions</t>
+          <t>Research Associate (m/f/d)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Biological sciences » Biology Biological sciences » Zoology</t>
+          <t>Engineering » Electrical engineering Engineering » Electronic engineering Computer science » Other</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -540,54 +540,54 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446779</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446923</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21 June 2026</t>
+          <t>22 June 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19 Jul 2026 - 21:59 (UTC)</t>
+          <t>10 Jul 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>University of Cologne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Postdoc In Photonic Chips for Integrated Raman Sensing</t>
+          <t>10 Doctoral Researchers / Doctoral positions (f/m/d) - Plant Ecological Genetics</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Engineering » Electronic engineering Engineering » Microengineering Physics » Optics</t>
+          <t>Biological sciences » Botany Biological sciences » Other</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,12 +597,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446780</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446943</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Wageningen University and Research Centre via AcademicTransfer</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PhD Position Coronary Vasomotor Dysfunction &amp; Early Detection in ANOCA Patients</t>
+          <t>Postdoc: Evolution of Taste Receptors in Specialist Insect–Plant Interactions</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Medical sciences » Medicine</t>
+          <t>Biological sciences » Biology Biological sciences » Zoology</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446781</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446779</t>
         </is>
       </c>
     </row>
@@ -676,32 +676,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:14 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Research Engineer / Postdoc in Biomedical AI for Public Health Communication (f/m/x)</t>
+          <t>Postdoc In Photonic Chips for Integrated Raman Sensing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Medical sciences</t>
+          <t>Engineering » Electronic engineering Engineering » Microengineering Physics » Optics</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446782</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446780</t>
         </is>
       </c>
     </row>
@@ -728,37 +728,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20 June 2026</t>
+          <t>21 June 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11 Aug 2026 - 21:59 (UTC)</t>
+          <t>10 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uppsala Universitet via MyNetwork</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Assistant Professor in Engineering Sciences</t>
+          <t>PhD Position Coronary Vasomotor Dysfunction &amp; Early Detection in ANOCA Patients</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Medical sciences » Medicine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446619</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446781</t>
         </is>
       </c>
     </row>
@@ -785,37 +785,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20 June 2026</t>
+          <t>21 June 2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:14 (UTC)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Postdoc in soil biodiversity analysis across Europe</t>
+          <t>Research Engineer / Postdoc in Biomedical AI for Public Health Communication (f/m/x)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446629</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446782</t>
         </is>
       </c>
     </row>
@@ -847,32 +847,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2 Jul 2026 - 21:59 (UTC)</t>
+          <t>11 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wageningen University and Research Centre via AcademicTransfer</t>
+          <t>Uppsala Universitet via MyNetwork</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PhD in Optimizing Canopy Photosynthesis in controlled environment agriculture</t>
+          <t>Assistant Professor in Engineering Sciences</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Agronomics Agricultural sciences » Phytotechny</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446637</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446619</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15 Jul 2026 - 21:59 (UTC)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -914,22 +914,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maastricht University via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PhD Candidate Advanced System Modelling for Circular Plastics Recycling</t>
+          <t>Postdoc in soil biodiversity analysis across Europe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Computer science » Modelling tools Engineering » Chemical engineering Engineering » Process engineering</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446623</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446629</t>
         </is>
       </c>
     </row>
@@ -961,32 +961,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>2 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Wageningen University and Research Centre via AcademicTransfer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Postdoc in 6G Radio Digital Twin-assisted Situation-aware ISAC D-MIMO for Resilient and Efficient ITS and NTN</t>
+          <t>PhD in Optimizing Canopy Photosynthesis in controlled environment agriculture</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Engineering » Other Mathematics » Applied mathematics Technology » Telecommunications technology</t>
+          <t>Agricultural sciences » Agronomics Agricultural sciences » Phytotechny</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Automotive Control</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446737</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446637</t>
         </is>
       </c>
     </row>
@@ -1018,27 +1018,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Karlstad University</t>
+          <t>Maastricht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doctoral student in Computer Science</t>
+          <t>PhD Candidate Advanced System Modelling for Circular Plastics Recycling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Computer science</t>
+          <t>Computer science » Modelling tools Engineering » Chemical engineering Engineering » Process engineering</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446677</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446623</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17 Sep 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1090,17 +1090,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PhD Position in AI for Materials Modeling</t>
+          <t>Postdoc in 6G Radio Digital Twin-assisted Situation-aware ISAC D-MIMO for Resilient and Efficient ITS and NTN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chemistry » Computational chemistry Computer science » Other Engineering » Materials engineering Engineering » Other Physics » Computational physics Physics » Other</t>
+          <t>Computer science » Other Engineering » Electrical engineering Engineering » Other Mathematics » Applied mathematics Technology » Telecommunications technology</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1110,19 +1110,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Automotive Control</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446742</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446737</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1132,27 +1132,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16 Jul 2026 - 14:34 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Karlstad University</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doctoral Researcher - CAR T Cell Therapy Development</t>
+          <t>Doctoral student in Computer Science</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Medical sciences</t>
+          <t>Computer science</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1167,19 +1167,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446642</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446677</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1189,27 +1189,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17 Jul 2026 - 06:33 (UTC)</t>
+          <t>17 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PhD position in “Molecular Microbial Ecology focusing on phage-host interactions” (x/d/f/m)</t>
+          <t>PhD Position in AI for Materials Modeling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Environmental science</t>
+          <t>Chemistry » Computational chemistry Computer science » Other Engineering » Materials engineering Engineering » Other Physics » Computational physics Physics » Other</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446643</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446742</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12 Jul 2026 - 21:00 (UTC)</t>
+          <t>16 Jul 2026 - 14:34 (UTC)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1261,17 +1261,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher (m/f/d) Self-Driving Lab for the Discovery of Novel Catalyst Materials</t>
+          <t>Doctoral Researcher - CAR T Cell Therapy Development</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446644</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446642</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>17 Jul 2026 - 06:33 (UTC)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1318,17 +1318,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Postdoc (Physics) – ³He and neutron polarization methods</t>
+          <t>PhD position in “Molecular Microbial Ecology focusing on phage-host interactions” (x/d/f/m)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Environmental science</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446645</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446643</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>12 Jul 2026 - 21:00 (UTC)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PhD Position - Active Matter and Machine Learning</t>
+          <t>Postdoctoral Researcher (m/f/d) Self-Driving Lab for the Discovery of Novel Catalyst Materials</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446646</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446644</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in Quantum Algorithms</t>
+          <t>Postdoc (Physics) – ³He and neutron polarization methods</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446647</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446645</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Student Research Assistant – Polymer &amp; Membrane Materials for Next Generation Energy Technologies</t>
+          <t>PhD Position - Active Matter and Machine Learning</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1514,49 +1514,49 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446648</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446646</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PhD in Simulation-integrated strategy for polymers in integrated circuit packaging</t>
+          <t>Postdoctoral Researcher in Quantum Algorithms</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering Engineering » Mechanical engineering</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1571,49 +1571,49 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443230</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446647</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9 June 2026</t>
+          <t>20 June 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PhD in Flexibility Services from Electrified Process Industry: A Focus on Steam-Heated Processes</t>
+          <t>Student Research Assistant – Polymer &amp; Membrane Materials for Next Generation Energy Technologies</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Process engineering</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443214</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446648</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3 Aug 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1655,22 +1655,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Postdoc Safe Waterborne Digital Systems</t>
+          <t>PhD in Simulation-integrated strategy for polymers in integrated circuit packaging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Maritime engineering</t>
+          <t>Engineering » Materials engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443221</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443230</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PhD in AI-driven Fair Energy Curtailment Policies</t>
+          <t>PhD in Flexibility Services from Electrified Process Industry: A Focus on Steam-Heated Processes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Electrical engineering</t>
+          <t>Engineering » Electrical engineering Engineering » Process engineering</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443208</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443214</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>3 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Postdoc Tx/Rx Isolation Measurements of FMCW radar using a reverberation chamber (TRIM)</t>
+          <t>Postdoc Safe Waterborne Digital Systems</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Electronic engineering</t>
+          <t>Engineering » Control engineering Engineering » Maritime engineering</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Automotive Control</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443225</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443221</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>28 Jun 2026 - 21:59 (UTC)</t>
+          <t>8 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1826,17 +1826,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PhD Position on Strengthening Mortgage Portfolio Resilience to Physical Climate Risks</t>
+          <t>PhD in AI-driven Fair Energy Curtailment Policies</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Economics » Environmental economics Economics » Financial science Engineering » Civil engineering Engineering » Simulation engineering</t>
+          <t>Engineering » Control engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443209</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443208</t>
         </is>
       </c>
     </row>
@@ -1888,17 +1888,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Privacy-Preserving AI and Knowledge Graphs for Energy Digital Twins</t>
+          <t>Postdoc Tx/Rx Isolation Measurements of FMCW radar using a reverberation chamber (TRIM)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Computer science » Programming</t>
+          <t>Engineering » Electrical engineering Engineering » Electronic engineering</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Automotive Control</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443229</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443225</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8 May 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 21:59 (UTC)</t>
+          <t>28 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Professor in Chemical Engineering</t>
+          <t>PhD Position on Strengthening Mortgage Portfolio Resilience to Physical Climate Risks</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Engineering » Chemical engineering</t>
+          <t>Economics » Environmental economics Economics » Financial science Engineering » Civil engineering Engineering » Simulation engineering</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/434598</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443209</t>
         </is>
       </c>
     </row>
@@ -1982,32 +1982,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8 May 2026</t>
+          <t>9 June 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4 Aug 2026 - 21:59 (UTC)</t>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doctoral position on PFAS Pathways: Tracking “Forever Chemicals” through Soil–Groundwater Interfaces for Safer Water</t>
+          <t>Privacy-Preserving AI and Knowledge Graphs for Energy Digital Twins</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Soil science Chemistry » Analytical chemistry Chemistry » Other Computer science » Other Environmental science » Earth science Environmental science » Water science Environmental science » Other</t>
+          <t>Computer science » Programming</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/434621</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443229</t>
         </is>
       </c>
     </row>
@@ -2039,37 +2039,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8 June 2026</t>
+          <t>8 May 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>22 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher (f_m_x) – Adaptive Digital Twin Prototypes for EGS Systems</t>
+          <t>Professor in Chemical Engineering</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Geosciences</t>
+          <t>Engineering » Chemical engineering</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>Leading Researcher (R4)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443018</t>
+          <t>https://euraxess.ec.europa.eu/jobs/434598</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8 June 2026</t>
+          <t>8 May 2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>4 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PhD Thesis - In situ TEM of Coulomb phase excitation in artificial spin ice matter</t>
+          <t>Doctoral position on PFAS Pathways: Tracking “Forever Chemicals” through Soil–Groundwater Interfaces for Safer Water</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Agricultural sciences » Soil science Chemistry » Analytical chemistry Chemistry » Other Computer science » Other Environmental science » Earth science Environmental science » Water science Environmental science » Other</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443014</t>
+          <t>https://euraxess.ec.europa.eu/jobs/434621</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Engineer for Laboratory Automation – AI Driven Photovoltaic Research</t>
+          <t>Postdoctoral Researcher (f_m_x) – Adaptive Digital Twin Prototypes for EGS Systems</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Geosciences</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443028</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443018</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4 Jul 2026 - 22:00 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PhD Student (f/m/d) Upscaling Particle-Based Separation Models: Bridging Laboratory and Industrial Flotation Processes / Completed university studies (Master/Diploma) in the field of Chemical/Metallurgical/(Mineral) Process Engineering …</t>
+          <t>PhD Thesis - In situ TEM of Coulomb phase excitation in artificial spin ice matter</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443042</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443014</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>26 Jun 2026 - 04:11 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Postdoc in "Human Decisions in Environmental Systems" (f/d/m/x) (HIPP 27.4)</t>
+          <t>Engineer for Laboratory Automation – AI Driven Photovoltaic Research</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Environmental science</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443030</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443028</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>26 Jun 2026 - 04:24 (UTC)</t>
+          <t>4 Jul 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2344,17 +2344,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Postdoc in "Science Narratives" (m/d/f/x) (HIPP 27.5)</t>
+          <t>PhD Student (f/m/d) Upscaling Particle-Based Separation Models: Bridging Laboratory and Industrial Flotation Processes / Completed university studies (Master/Diploma) in the field of Chemical/Metallurgical/(Mineral) Process Engineering …</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Environmental science</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443032</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443042</t>
         </is>
       </c>
     </row>
@@ -2381,37 +2381,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7 May 2026</t>
+          <t>8 June 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20 Jun 2026 - 21:59 (UTC)</t>
+          <t>26 Jun 2026 - 04:11 (UTC)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Postdoc in optical quantum networks</t>
+          <t>Postdoc in "Human Decisions in Environmental Systems" (f/d/m/x) (HIPP 27.4)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Engineering » Other Physics » Optics Physics » Quantum mechanics Physics » Other</t>
+          <t>Environmental science</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/434335</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443030</t>
         </is>
       </c>
     </row>
@@ -2438,37 +2438,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7 February 2026</t>
+          <t>8 June 2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>26 Jun 2026 - 04:24 (UTC)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Postdoc on Continuous Optical Clocks</t>
+          <t>Postdoc in "Science Narratives" (m/d/f/x) (HIPP 27.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Physics » Optics Physics » Quantum mechanics</t>
+          <t>Environmental science</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/408015</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443032</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2495,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6 June 2026</t>
+          <t>7 May 2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>20 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doctoral student in Grid Impact Assessment of Optimized Energy Communities</t>
+          <t>Postdoc in optical quantum networks</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Engineering » Other Technology » Energy technology Technology » Environmental technology</t>
+          <t>Computer science » Other Engineering » Electrical engineering Engineering » Other Physics » Optics Physics » Quantum mechanics Physics » Other</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442914</t>
+          <t>https://euraxess.ec.europa.eu/jobs/434335</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6 June 2026</t>
+          <t>7 February 2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>15 Aug 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2567,22 +2567,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Head of Analytical Laboratories/Senior MC-ICP-MS Specialist in Isotope Geochemistry</t>
+          <t>Postdoc on Continuous Optical Clocks</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chemistry » Analytical chemistry Chemistry » Other Environmental science » Earth science Environmental science » Other</t>
+          <t>Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442916</t>
+          <t>https://euraxess.ec.europa.eu/jobs/408015</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3 Sep 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PhD position in Multi-State Programmable Robotic Matter</t>
+          <t>Doctoral student in Grid Impact Assessment of Optimized Energy Communities</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chemistry » Other Engineering » Chemical engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Other</t>
+          <t>Engineering » Other Technology » Energy technology Technology » Environmental technology</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442917</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442914</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3 Sep 2026 - 21:59 (UTC)</t>
+          <t>15 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PhD position in Biohybrid Robotics</t>
+          <t>Head of Analytical Laboratories/Senior MC-ICP-MS Specialist in Isotope Geochemistry</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Biological sciences » Other Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Systems engineering Engineering » Other</t>
+          <t>Chemistry » Analytical chemistry Chemistry » Other Environmental science » Earth science Environmental science » Other</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442922</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442916</t>
         </is>
       </c>
     </row>
@@ -2723,37 +2723,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6 February 2026</t>
+          <t>6 June 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>3 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Postdoc on Quantum Simulation &amp; Computing with Single Sr Atoms in Optical Tweezers</t>
+          <t>PhD position in Multi-State Programmable Robotic Matter</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Physics » Optics Physics » Quantum mechanics</t>
+          <t>Chemistry » Other Engineering » Chemical engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/407551</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442917</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>6 June 2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
+          <t>3 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2795,17 +2795,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paul Scherrer Institut Villigen</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PhD Student in Probabilistic Modelling of Severe Nuclear Accident Risk (Index-Nr. 4103-28180)</t>
+          <t>PhD position in Biohybrid Robotics</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Engineering » Nuclear engineering Engineering » Chemical engineering Engineering » Mechanical engineering</t>
+          <t>Biological sciences » Other Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Systems engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/433719</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442922</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>6 February 2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>15 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Postdoc Real-World Testing of Future In-Vehicle Touchscreens</t>
+          <t>Postdoc on Quantum Simulation &amp; Computing with Single Sr Atoms in Optical Tweezers</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Mechanical engineering</t>
+          <t>Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442540</t>
+          <t>https://euraxess.ec.europa.eu/jobs/407551</t>
         </is>
       </c>
     </row>
@@ -2894,32 +2894,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5 June 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Paul Scherrer Institut Villigen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PhD Position Delocalized Quantum Magnetism in Atomic Spin Assemblies</t>
+          <t>PhD Student in Probabilistic Modelling of Severe Nuclear Accident Risk (Index-Nr. 4103-28180)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
+          <t>Engineering » Nuclear engineering Engineering » Chemical engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442548</t>
+          <t>https://euraxess.ec.europa.eu/jobs/433719</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PhD Position Spin-Wave Generation in Quantum Materials</t>
+          <t>Postdoc Real-World Testing of Future In-Vehicle Touchscreens</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
+          <t>Engineering » Control engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442549</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442540</t>
         </is>
       </c>
     </row>
@@ -3013,27 +3013,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 21:59 (UTC)</t>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doctoral student in SiC bipolar devices for power electronics</t>
+          <t>PhD Position Delocalized Quantum Magnetism in Atomic Spin Assemblies</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Other Technology » Energy technology</t>
+          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442633</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442548</t>
         </is>
       </c>
     </row>
@@ -3070,32 +3070,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 Sep 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Postdoc in simulation model development for climate-neutral waterborne transport on coastal and inland waterways</t>
+          <t>PhD Position Spin-Wave Generation in Quantum Materials</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Engineering » Mechanical engineering Engineering » Systems engineering Engineering » Other Physics » Other Technology » Energy technology Technology » Environmental technology Technology » Transport technology</t>
+          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442646</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442549</t>
         </is>
       </c>
     </row>
@@ -3127,27 +3127,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PhD in Computer Architecture for Real-Time AI at the Edge</t>
+          <t>Doctoral student in SiC bipolar devices for power electronics</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Computer science » Computer architecture Computer science » Computer hardware</t>
+          <t>Engineering » Electrical engineering Engineering » Other Technology » Energy technology</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442550</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442633</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3194,22 +3194,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Uppsala Universitet via MyNetwork</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PhD student in Machine Learning with a focus on mathematical foundations of uncertainty quantification in deep learning</t>
+          <t>Postdoc in simulation model development for climate-neutral waterborne transport on coastal and inland waterways</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Computer science Technology</t>
+          <t>Engineering » Mechanical engineering Engineering » Systems engineering Engineering » Other Physics » Other Technology » Energy technology Technology » Environmental technology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442538</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442646</t>
         </is>
       </c>
     </row>
@@ -3241,28 +3241,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>7 Aug 2026 - 12:00 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Talentech</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Postdoc in stretchable fluid batteries for sustainable wearable electronics</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>PhD in Computer Architecture for Real-Time AI at the Edge</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Computer science » Computer architecture Computer science » Computer hardware</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3272,12 +3276,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442536</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442550</t>
         </is>
       </c>
     </row>
@@ -3294,27 +3298,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>16 Jul 2026 - 23:19 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>myScience</t>
+          <t>Uppsala Universitet via MyNetwork</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doctorante</t>
+          <t>PhD student in Machine Learning with a focus on mathematical foundations of uncertainty quantification in deep learning</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pharmacological sciences Medical sciences</t>
+          <t>Computer science Technology</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3329,12 +3333,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442537</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442538</t>
         </is>
       </c>
     </row>
@@ -3351,32 +3355,28 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2 Jul 2026 - 21:59 (UTC)</t>
+          <t>7 Aug 2026 - 12:00 (UTC)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Talentech</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Assistant Professor on Network Science</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Engineering » Computer engineering Engineering » Electrical engineering</t>
-        </is>
-      </c>
+          <t>Postdoc in stretchable fluid batteries for sustainable wearable electronics</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442547</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442536</t>
         </is>
       </c>
     </row>
@@ -3408,32 +3408,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>15 Aug 2026 - 21:59 (UTC)</t>
+          <t>16 Jul 2026 - 23:19 (UTC)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>myScience</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Assistant Professors in Language and AI Engineering</t>
+          <t>Doctorante</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Computer science Language sciences » Linguistics</t>
+          <t>Pharmacological sciences Medical sciences</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442542</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442537</t>
         </is>
       </c>
     </row>
@@ -3460,37 +3460,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4 May 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
+          <t>2 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paul Scherrer Institut Villigen</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PhD Student in the Development of Models for Droplet Behaviour in PWRs (Index-Nr. 4103-27812)</t>
+          <t>Assistant Professor on Network Science</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Engineering » Mechanical engineering Engineering » Nuclear engineering Physics Mathematics » Applied mathematics</t>
+          <t>Engineering » Computer engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/433442</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442547</t>
         </is>
       </c>
     </row>
@@ -3517,37 +3517,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>5 June 2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Postdoc in LLM Agents for Research Automation</t>
+          <t>Assistant Professors in Language and AI Engineering</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other</t>
+          <t>Computer science Language sciences » Linguistics</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Automotive Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442359</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442542</t>
         </is>
       </c>
     </row>
@@ -3574,37 +3574,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4 June 2026</t>
+          <t>4 May 2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Paul Scherrer Institut Villigen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Post-doc in bio-fuel production using experiments and AI-assisted analysis</t>
+          <t>PhD Student in the Development of Models for Droplet Behaviour in PWRs (Index-Nr. 4103-27812)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chemistry » Other Computer science » Other Engineering » Chemical engineering Engineering » Other Technology » Energy technology</t>
+          <t>Engineering » Mechanical engineering Engineering » Nuclear engineering Physics Mathematics » Applied mathematics</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442363</t>
+          <t>https://euraxess.ec.europa.eu/jobs/433442</t>
         </is>
       </c>
     </row>
@@ -3636,32 +3636,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 12:00 (Europe/Berlin)</t>
+          <t>3 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Continuum Mechanics Group - TUM</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Postdoc Position on Physics-informed Generative Modeling and Multiscale Learning (m/w/d)</t>
+          <t>Postdoc in LLM Agents for Research Automation</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Simulation engineering Engineering</t>
+          <t>Computer science » Programming Computer science » Other</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3671,12 +3671,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Automotive Control</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442500</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442359</t>
         </is>
       </c>
     </row>
@@ -3693,32 +3693,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 13:12 (Europe/Berlin)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Continuum Mechanics Group - TUM</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ph.D. Position on Physics-informed Generative Modeling and Multiscale Learning</t>
+          <t>Post-doc in bio-fuel production using experiments and AI-assisted analysis</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Simulation engineering Mathematics » Computational mathematics</t>
+          <t>Chemistry » Other Computer science » Other Engineering » Chemical engineering Engineering » Other Technology » Energy technology</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442498</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442363</t>
         </is>
       </c>
     </row>
@@ -3750,32 +3750,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>24 Jun 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 12:00 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Continuum Mechanics Group - TUM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Postdoctoral researcher Evaluating Methodologies for Urban Resilience</t>
+          <t>Postdoc Position on Physics-informed Generative Modeling and Multiscale Learning (m/w/d)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sociology » Urban sociology</t>
+          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Simulation engineering Engineering</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442256</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442500</t>
         </is>
       </c>
     </row>
@@ -3807,27 +3807,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 Sep 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 13:12 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Continuum Mechanics Group - TUM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PhD Position in Infrastructure Intervention Effectiveness Analysis for Road Safety</t>
+          <t>Ph.D. Position on Physics-informed Generative Modeling and Multiscale Learning</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Architecture » Other Technology » Transport technology</t>
+          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Simulation engineering Mathematics » Computational mathematics</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442360</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442498</t>
         </is>
       </c>
     </row>
@@ -3864,32 +3864,32 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1 Sep 2026 - 21:59 (UTC)</t>
+          <t>24 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PhD Position in Vehicle Sensor and Remote Sensing Analysis for Road Safety</t>
+          <t>Postdoctoral researcher Evaluating Methodologies for Urban Resilience</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Civil engineering Engineering » Other Environmental science » Earth science Technology » Transport technology</t>
+          <t>Sociology » Urban sociology</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442361</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442256</t>
         </is>
       </c>
     </row>
@@ -3916,32 +3916,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>31 October 2025</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>31 Dec 2029 - 23:59 (Europe/Berlin)</t>
+          <t>1 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Makino Europe GmbH</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Internship Industrial Research Metal Cutting Monitoring and Simulation</t>
+          <t>PhD Position in Infrastructure Intervention Effectiveness Analysis for Road Safety</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Engineering » Simulation engineering Engineering » Mechanical engineering</t>
+          <t>Architecture » Other Technology » Transport technology</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Automotive Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/384615</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442360</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>31 May 2026</t>
+          <t>4 June 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 21:59 (UTC)</t>
+          <t>1 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doctoral student in Electrical Engineering focusing on Machine Learning</t>
+          <t>PhD Position in Vehicle Sensor and Remote Sensing Analysis for Road Safety</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering</t>
+          <t>Computer science » Other Engineering » Civil engineering Engineering » Other Environmental science » Earth science Technology » Transport technology</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441319</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442361</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30 May 2026</t>
+          <t>31 October 2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 21:59 (UTC)</t>
+          <t>31 Dec 2029 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Makino Europe GmbH</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PhD position: aboveground-belowground linkages in beech masting dynamics - NIOO-KNAW - Wageningen</t>
+          <t>Internship Industrial Research Metal Cutting Monitoring and Simulation</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Engineering » Simulation engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Automotive Control</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441155</t>
+          <t>https://euraxess.ec.europa.eu/jobs/384615</t>
         </is>
       </c>
     </row>
@@ -4087,27 +4087,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30 May 2026</t>
+          <t>31 May 2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>25 Jul 2026 - 21:59 (UTC)</t>
+          <t>22 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Junior Researcher Smart Charging &amp; Vehicle-to-Grid (V2G)</t>
+          <t>Doctoral student in Electrical Engineering focusing on Machine Learning</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441152</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441319</t>
         </is>
       </c>
     </row>
@@ -4144,37 +4144,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3 June 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 23:59 (Europe/Berlin)</t>
+          <t>22 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ruhr University Bochum</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Three-year Postdoc (m/f/d) in X-ray photoemission spectroscopy of lithium batteries (TV-L 13 100%)</t>
+          <t>PhD position: aboveground-belowground linkages in beech masting dynamics - NIOO-KNAW - Wageningen</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1) Recognised Researcher (R2) Established Researcher (R3) Leading Researcher (R4)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442179</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441155</t>
         </is>
       </c>
     </row>
@@ -4201,33 +4201,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3 June 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>23 Jun 2026 - 12:00 (UTC)</t>
+          <t>25 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Talentech</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PhD in Plant Bioelectronics</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>Junior Researcher Smart Charging &amp; Vehicle-to-Grid (V2G)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Engineering » Electrical engineering</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4237,12 +4241,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441871</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441152</t>
         </is>
       </c>
     </row>
@@ -4259,32 +4263,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
+          <t>5 Jul 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Idiap Research Institute</t>
+          <t>Ruhr University Bochum</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher: Trustworthy &amp; Privacy-Preserving Identity Technologies F/M</t>
+          <t>Three-year Postdoc (m/f/d) in X-ray photoemission spectroscopy of lithium batteries (TV-L 13 100%)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Computer science</t>
+          <t>Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>First Stage Researcher (R1) Recognised Researcher (R2) Established Researcher (R3) Leading Researcher (R4)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4294,12 +4298,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/442142</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442179</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4320,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 21:59 (UTC)</t>
+          <t>23 Jun 2026 - 12:00 (UTC)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4326,19 +4330,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Karolinska Institutet via Varbi</t>
+          <t>Talentech</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Assistant Professor in Data-Driven Cardiovascular Medicine</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Medical sciences » Medicine</t>
-        </is>
-      </c>
+          <t>PhD in Plant Bioelectronics</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>First Stage Researcher (R1)</t>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441909</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441871</t>
         </is>
       </c>
     </row>
@@ -4373,32 +4373,32 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2 Aug 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 23:59 (Europe/Zurich)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Idiap Research Institute</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Assistant Professor In Formal Methods and Neuro-Symbolic AI</t>
+          <t>Postdoctoral Researcher: Trustworthy &amp; Privacy-Preserving Identity Technologies F/M</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Computer science » Autonomic computing Computer science » Cybernetics</t>
+          <t>Computer science</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441881</t>
+          <t>https://euraxess.ec.europa.eu/jobs/442142</t>
         </is>
       </c>
     </row>
@@ -4425,37 +4425,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>3 June 2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Karolinska Institutet via Varbi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Postdoc Recycling of Lithium Iron Phosphate Batteries</t>
+          <t>Assistant Professor in Data-Driven Cardiovascular Medicine</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Engineering » Chemical engineering Engineering » Process engineering</t>
+          <t>Medical sciences » Medicine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440768</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441909</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>3 June 2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>20 Jun 2026 - 22:00 (UTC)</t>
+          <t>2 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4497,22 +4497,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>University of Groningen via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PhD position Sensors for Neuromorphic Touch in Adaptive Robotic Grasping</t>
+          <t>Assistant Professor In Formal Methods and Neuro-Symbolic AI</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Mechanical engineering</t>
+          <t>Computer science » Autonomic computing Computer science » Cybernetics</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440782</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441881</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>20 Jun 2026 - 22:00 (UTC)</t>
+          <t>21 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4554,22 +4554,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>University of Groningen via AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PhD position Neuromorphic sensing &amp; control for bionic lower limbs</t>
+          <t>Postdoc Recycling of Lithium Iron Phosphate Batteries</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Computer science » Cybernetics Computer science » Programming Engineering » Biomedical engineering Engineering » Electrical engineering</t>
+          <t>Engineering » Chemical engineering Engineering » Process engineering</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440781</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440768</t>
         </is>
       </c>
     </row>
@@ -4596,32 +4596,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>20 Jun 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Groningen via AcademicTransfer</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doctoral student in Interpretable and Experience-Driven Learning for Collaborative Robots</t>
+          <t>PhD position Sensors for Neuromorphic Touch in Adaptive Robotic Grasping</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other Engineering » Control engineering Engineering » Electrical engineering Engineering » Systems engineering Engineering » Other Mathematics » Applied mathematics</t>
+          <t>Engineering » Electrical engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440490</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440782</t>
         </is>
       </c>
     </row>
@@ -4653,37 +4653,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>26 Jun 2026 - 21:59 (UTC)</t>
+          <t>20 Jun 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Groningen via AcademicTransfer</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Postdoc in Trustworthy DevOps for autonomous vehicles</t>
+          <t>PhD position Neuromorphic sensing &amp; control for bionic lower limbs</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Systems engineering Engineering » Other</t>
+          <t>Computer science » Cybernetics Computer science » Programming Engineering » Biomedical engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Automotive Control</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440482</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440781</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>8 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4725,22 +4725,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Karolinska Institutet via Varbi</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Postdoctoral studies in in molecular signature of vascular cognitive impairment and dementia (scholarship)</t>
+          <t>Doctoral student in Interpretable and Experience-Driven Learning for Collaborative Robots</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Medical sciences</t>
+          <t>Computer science » Programming Computer science » Other Engineering » Control engineering Engineering » Electrical engineering Engineering » Systems engineering Engineering » Other Mathematics » Applied mathematics</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440390</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440490</t>
         </is>
       </c>
     </row>
@@ -4772,27 +4772,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 23:00 (UTC)</t>
+          <t>26 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>jobRxiv</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Postdoc - Lab Automation and Data-Driven Colloid Science</t>
+          <t>Postdoc in Trustworthy DevOps for autonomous vehicles</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Engineering » Control engineering Engineering » Systems engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Automotive Control</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440399</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440482</t>
         </is>
       </c>
     </row>
@@ -4829,32 +4829,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>24 Aug 2026 - 21:59 (UTC)</t>
+          <t>8 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Karolinska Institutet via Varbi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doctoral position in landscape ecology and geospatial analysis</t>
+          <t>Postdoctoral studies in in molecular signature of vascular cognitive impairment and dementia (scholarship)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Environmental science » Earth science Environmental science » Ecology Environmental science » Other Geography » Human geography Geography » Other</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440484</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440390</t>
         </is>
       </c>
     </row>
@@ -4886,32 +4886,32 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>24 Aug 2026 - 21:59 (UTC)</t>
+          <t>21 Jun 2026 - 23:00 (UTC)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>jobRxiv</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doctoral position in social indicator development with text-based and spatial data</t>
+          <t>Postdoc - Lab Automation and Data-Driven Colloid Science</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Architecture » Other Environmental science » Earth science Geography » Human geography Sociology » Urban sociology Sociology » Other</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/440485</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440399</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>28 January 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>26 Jun 2026 - 21:59 (UTC)</t>
+          <t>24 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Doctoral Researcher in Food Processing for Planetary and Human Health</t>
+          <t>Doctoral position in landscape ecology and geospatial analysis</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Other Engineering » Other Technology » Biotechnology</t>
+          <t>Environmental science » Earth science Environmental science » Ecology Environmental science » Other Geography » Human geography Geography » Other</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/404614</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440484</t>
         </is>
       </c>
     </row>
@@ -4995,32 +4995,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>23 Jun 2026 - 21:59 (UTC)</t>
+          <t>24 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RWTH Aachen University</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Research Assistant/Associate (f/m/d) - V000011054</t>
+          <t>Doctoral position in social indicator development with text-based and spatial data</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architecture » Other Environmental science » Earth science Geography » Human geography Sociology » Urban sociology Sociology » Other</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/439798</t>
+          <t>https://euraxess.ec.europa.eu/jobs/440485</t>
         </is>
       </c>
     </row>
@@ -5052,32 +5052,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>28 January 2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 21:59 (UTC)</t>
+          <t>26 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PhD Position Systemic Risk in Climate-Sensitive Housing Markets</t>
+          <t>Doctoral Researcher in Food Processing for Planetary and Human Health</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Environmental science » Global change Environmental science » Natural resources management</t>
+          <t>Agricultural sciences » Other Engineering » Other Technology » Biotechnology</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/439739</t>
+          <t>https://euraxess.ec.europa.eu/jobs/404614</t>
         </is>
       </c>
     </row>
@@ -5109,37 +5109,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>26 April 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>24 Jun 2026 - 21:59 (UTC)</t>
+          <t>23 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>RWTH Aachen University</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Postdoc in Cognitive Science (3 years)</t>
+          <t>Research Assistant/Associate (f/m/d) - V000011054</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neurosciences » Neuropsychology Psychological sciences » Cognitive science Psychological sciences » Psychology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/431660</t>
+          <t>https://euraxess.ec.europa.eu/jobs/439798</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24 September 2025</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 23:59 (Europe/Amsterdam)</t>
+          <t>22 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5181,17 +5181,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fraunhofer ICT</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PhD Position: Electrodes for hydrogen-iron flow batteries</t>
+          <t>PhD Position Systemic Risk in Climate-Sensitive Housing Markets</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Engineering » Chemical engineering</t>
+          <t>Environmental science » Global change Environmental science » Natural resources management</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/375876</t>
+          <t>https://euraxess.ec.europa.eu/jobs/439739</t>
         </is>
       </c>
     </row>
@@ -5223,37 +5223,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>26 April 2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 21:59 (UTC)</t>
+          <t>24 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Assistant Professor in Predictive Modelling and Simulation of Rotorcraft and VTOL Aircraft</t>
+          <t>Postdoc in Cognitive Science (3 years)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Engineering » Aerospace engineering Engineering » Simulation engineering</t>
+          <t>Neurosciences » Neuropsychology Psychological sciences » Cognitive science Psychological sciences » Psychology</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/439041</t>
+          <t>https://euraxess.ec.europa.eu/jobs/431660</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>24 September 2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>22 Jun 2026 - 23:59 (Europe/Amsterdam)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5295,17 +5295,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Fraunhofer ICT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PhD-position: Biominerals, Crystals and Climate</t>
+          <t>PhD Position: Electrodes for hydrogen-iron flow batteries</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Biological sciences » Other Chemistry » Analytical chemistry Chemistry » Biochemistry Chemistry » Inorganic chemistry Chemistry » Other Environmental science » Earth science</t>
+          <t>Engineering » Chemical engineering</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/439148</t>
+          <t>https://euraxess.ec.europa.eu/jobs/375876</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>23 January 2026</t>
+          <t>23 May 2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>21 Jul 2026 - 06:04 (UTC)</t>
+          <t>21 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5352,22 +5352,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Postdoc on Stable Optical Circuits for Quantum Technology</t>
+          <t>Assistant Professor in Predictive Modelling and Simulation of Rotorcraft and VTOL Aircraft</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Physics » Optics Physics » Quantum mechanics</t>
+          <t>Engineering » Aerospace engineering Engineering » Simulation engineering</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/403411</t>
+          <t>https://euraxess.ec.europa.eu/jobs/439041</t>
         </is>
       </c>
     </row>
@@ -5394,17 +5394,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>23 April 2026</t>
+          <t>23 May 2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>21 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Postdoc position in light multiplexed, fiber-based artificial sensorimotor network</t>
+          <t>PhD-position: Biominerals, Crystals and Climate</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Engineering » Mechanical engineering Engineering » Other Physics » Other</t>
+          <t>Biological sciences » Other Chemistry » Analytical chemistry Chemistry » Biochemistry Chemistry » Inorganic chemistry Chemistry » Other Environmental science » Earth science</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/430919</t>
+          <t>https://euraxess.ec.europa.eu/jobs/439148</t>
         </is>
       </c>
     </row>
@@ -5451,12 +5451,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>23 January 2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>21 Jul 2026 - 06:04 (UTC)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5466,22 +5466,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PhD Position Unconventional Phased Array Topologies</t>
+          <t>Postdoc on Stable Optical Circuits for Quantum Technology</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Engineering » Communication engineering Engineering » Electrical engineering</t>
+          <t>Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438640</t>
+          <t>https://euraxess.ec.europa.eu/jobs/403411</t>
         </is>
       </c>
     </row>
@@ -5508,37 +5508,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>23 April 2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>21 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PhD Position Multi-Band Fusion in JCAS</t>
+          <t>Postdoc position in light multiplexed, fiber-based artificial sensorimotor network</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Engineering » Communication engineering Engineering » Electrical engineering</t>
+          <t>Engineering » Mechanical engineering Engineering » Other Physics » Other</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438641</t>
+          <t>https://euraxess.ec.europa.eu/jobs/430919</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>17 Nov 2026 - 15:54 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PhD: Lensless 3D optical imaging</t>
+          <t>PhD Position Unconventional Phased Array Topologies</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Engineering » Microengineering Physics » Applied physics Physics » Optics</t>
+          <t>Engineering » Communication engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438633</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438640</t>
         </is>
       </c>
     </row>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>22 January 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>17 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PhD Diagnostics for interconnected complex dynamical systems</t>
+          <t>PhD Position Multi-Band Fusion in JCAS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering</t>
+          <t>Engineering » Communication engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/403002</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438641</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 21:59 (UTC)</t>
+          <t>17 Nov 2026 - 15:54 (UTC)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5699,17 +5699,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Postdoc in Integrated Single-Photon Avalanche Diode Array for Quantum Computing</t>
+          <t>PhD: Lensless 3D optical imaging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Electronic engineering Physics » Optics Physics » Quantum mechanics</t>
+          <t>Engineering » Microengineering Physics » Applied physics Physics » Optics</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438297</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438633</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>22 January 2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>15 Nov 2026 - 20:33 (UTC)</t>
+          <t>17 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PhD - student: Machine learning for semiconductor wafer metrology</t>
+          <t>PhD Diagnostics for interconnected complex dynamical systems</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Engineering » Electronic engineering Engineering » Precision engineering</t>
+          <t>Engineering » Control engineering</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438306</t>
+          <t>https://euraxess.ec.europa.eu/jobs/403002</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>19 Jul 2026 - 21:59 (UTC)</t>
+          <t>21 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PhD in Physical control of a soft artificial heart</t>
+          <t>Postdoc in Integrated Single-Photon Avalanche Diode Array for Quantum Computing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering Engineering » Control engineering</t>
+          <t>Engineering » Electrical engineering Engineering » Electronic engineering Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438298</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438297</t>
         </is>
       </c>
     </row>
@@ -5850,32 +5850,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>17 Aug 2026 - 21:59 (UTC)</t>
+          <t>15 Nov 2026 - 20:33 (UTC)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PhD Students in Circular Economy and Climate Change Resilience</t>
+          <t>PhD - student: Machine learning for semiconductor wafer metrology</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Other Economics » Environmental economics Economics » Industrial economics Economics » Other Environmental science » Other Political sciences » Public policy</t>
+          <t>Computer science » Informatics Engineering » Electronic engineering Engineering » Precision engineering</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/438019</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438306</t>
         </is>
       </c>
     </row>
@@ -5907,12 +5907,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20 February 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>18 Aug 2026 - 11:01 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Reconstructing nanophotonic scattering geometries from their radiation pattern</t>
+          <t>PhD in Physical control of a soft artificial heart</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Physics » Metrology Physics » Optics</t>
+          <t>Engineering » Biomedical engineering Engineering » Control engineering</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/411838</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438298</t>
         </is>
       </c>
     </row>
@@ -5964,32 +5964,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>13 Jul 2026 - 21:59 (UTC)</t>
+          <t>17 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PhD Position Safe GPAI Planning, Decision-Making and Active Perception for Reliable Robot Autonomy</t>
+          <t>PhD Students in Circular Economy and Climate Change Resilience</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Engineering » Control engineering Engineering » Mechanical engineering</t>
+          <t>Agricultural sciences » Other Economics » Environmental economics Economics » Industrial economics Economics » Other Environmental science » Other Political sciences » Public policy</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441539</t>
+          <t>https://euraxess.ec.europa.eu/jobs/438019</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2 June 2026</t>
+          <t>20 February 2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>13 Jul 2026 - 21:59 (UTC)</t>
+          <t>18 Aug 2026 - 11:01 (UTC)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PhD Position Long-Term Reasoning and Adaptive Learning for Human-Aware Robot Autonomy</t>
+          <t>Reconstructing nanophotonic scattering geometries from their radiation pattern</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Engineering » Computer engineering Engineering » Control engineering</t>
+          <t>Physics » Metrology Physics » Optics</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441540</t>
+          <t>https://euraxess.ec.europa.eu/jobs/411838</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>13 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6098,17 +6098,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Postdoc Spin Transport in Mesoscopic Devices with Quantum Materials</t>
+          <t>PhD Position Safe GPAI Planning, Decision-Making and Active Perception for Reliable Robot Autonomy</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
+          <t>Engineering » Control engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441544</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441539</t>
         </is>
       </c>
     </row>
@@ -6140,27 +6140,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>22 Jun 2026 - 12:00 (UTC)</t>
+          <t>13 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Talentech</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PhD students in sensor fusion and optimal motion planning for drone swarms</t>
+          <t>PhD Position Long-Term Reasoning and Adaptive Learning for Human-Aware Robot Autonomy</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering » Computer engineering Engineering » Control engineering</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441533</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441540</t>
         </is>
       </c>
     </row>
@@ -6197,27 +6197,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1 Aug 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Karolinska Institutet via Varbi</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher in AI Modeling of Cellular Dynamics, Alpha Cell Program</t>
+          <t>Postdoc Spin Transport in Mesoscopic Devices with Quantum Materials</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neurosciences</t>
+          <t>Physics » Condensed matter properties Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441545</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441544</t>
         </is>
       </c>
     </row>
@@ -6254,27 +6254,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1 Sep 2026 - 21:59 (UTC)</t>
+          <t>22 Jun 2026 - 12:00 (UTC)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Talentech</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>PhD: AI-assisted discovery of chiral perovskites in nanophotonic environments</t>
+          <t>PhD students in sensor fusion and optimal motion planning for drone swarms</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Physics » Condensed matter properties Physics » Optics</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441536</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441533</t>
         </is>
       </c>
     </row>
@@ -6311,32 +6311,32 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>12 Sep 2026 - 22:00 (UTC)</t>
+          <t>1 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>University of Groningen via AcademicTransfer</t>
+          <t>Karolinska Institutet via Varbi</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PhD position in Moral Philosophy, Conceptual Engineering, and Ethics of Emerging Technologies</t>
+          <t>Postdoctoral Researcher in AI Modeling of Cellular Dynamics, Alpha Cell Program</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Philosophy » Ethics</t>
+          <t>Neurosciences</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/441542</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441545</t>
         </is>
       </c>
     </row>
@@ -6363,12 +6363,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6378,17 +6378,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>PhD Position on Life Cycle Assessment for Design of Structures</t>
+          <t>PhD: AI-assisted discovery of chiral perovskites in nanophotonic environments</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Engineering » Aerospace engineering Engineering » Mechanical engineering</t>
+          <t>Physics » Condensed matter properties Physics » Optics</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/437441</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441536</t>
         </is>
       </c>
     </row>
@@ -6420,32 +6420,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2 June 2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>12 Sep 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Groningen via AcademicTransfer</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Doctoral student in thermal packaging solutions for future communication and sensor systems</t>
+          <t>PhD position in Moral Philosophy, Conceptual Engineering, and Ethics of Emerging Technologies</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Engineering » Communication engineering Engineering » Electrical engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Other Physics » Electromagnetism Physics » Thermodynamics</t>
+          <t>Philosophy » Ethics</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446320</t>
+          <t>https://euraxess.ec.europa.eu/jobs/441542</t>
         </is>
       </c>
     </row>
@@ -6477,32 +6477,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>30 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Doctoral student in machine-learning for exploration of sustainable welding materials</t>
+          <t>PhD Position on Life Cycle Assessment for Design of Structures</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chemistry » Computational chemistry Chemistry » Physical chemistry Chemistry » Other Computer science » Other Engineering » Chemical engineering Engineering » Materials engineering Physics » Thermodynamics Physics » Other Technology » Energy technology</t>
+          <t>Engineering » Aerospace engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446323</t>
+          <t>https://euraxess.ec.europa.eu/jobs/437441</t>
         </is>
       </c>
     </row>
@@ -6539,32 +6539,32 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>13 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Postdoctoral fellow opening: Ambulatory Biomechanics, Sensor Fusion, and Machine Learning for Wearable Robotics</t>
+          <t>Doctoral student in thermal packaging solutions for future communication and sensor systems</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering Engineering » Control engineering</t>
+          <t>Engineering » Communication engineering Engineering » Electrical engineering Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Other Physics » Electromagnetism Physics » Thermodynamics</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446245</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446320</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 21:59 (UTC)</t>
+          <t>30 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6606,22 +6606,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Postdoctoral position in Biomedical Engineering with a focus on neuroengineering</t>
+          <t>Doctoral student in machine-learning for exploration of sustainable welding materials</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering</t>
+          <t>Chemistry » Computational chemistry Chemistry » Physical chemistry Chemistry » Other Computer science » Other Engineering » Chemical engineering Engineering » Materials engineering Physics » Thermodynamics Physics » Other Technology » Energy technology</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446297</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446323</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 21:59 (UTC)</t>
+          <t>13 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6668,17 +6668,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>PhD in Credible hybrid AI-mechanistic models for clinical decision-making: unveiling the untapped potential of sensitivity a...</t>
+          <t>Postdoctoral fellow opening: Ambulatory Biomechanics, Sensor Fusion, and Machine Learning for Wearable Robotics</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering Mathematics » Applied mathematics Medical sciences » Medicine</t>
+          <t>Engineering » Biomedical engineering Engineering » Control engineering</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446243</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446245</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>17 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6720,17 +6720,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Postdoc in AI-Driven Materials Discovery</t>
+          <t>Postdoctoral position in Biomedical Engineering with a focus on neuroengineering</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chemistry » Computational chemistry Computer science » Other Engineering » Materials engineering Engineering » Other Physics » Chemical physics Physics » Computational physics Physics » Other</t>
+          <t>Engineering » Biomedical engineering</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6745,12 +6745,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446319</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446297</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6777,22 +6777,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PhD Candidate in Agent-Based Modelling and Urban Health: Designing for Movement</t>
+          <t>PhD in Credible hybrid AI-mechanistic models for clinical decision-making: unveiling the untapped potential of sensitivity a...</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Engineering » Simulation engineering Environmental science » Global change Geography » Human geography Geography » Social geography</t>
+          <t>Engineering » Biomedical engineering Mathematics » Applied mathematics Medical sciences » Medicine</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) First Stage Researcher (R1)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446247</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446243</t>
         </is>
       </c>
     </row>
@@ -6824,32 +6824,32 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>16 Jul 2026 - 21:59 (UTC)</t>
+          <t>17 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>PhD position VIDI project With greater power must come great responsibility</t>
+          <t>Postdoc in AI-Driven Materials Discovery</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Juridical sciences » European law Juridical sciences » Informatic law</t>
+          <t>Chemistry » Computational chemistry Computer science » Other Engineering » Materials engineering Engineering » Other Physics » Chemical physics Physics » Computational physics Physics » Other</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446250</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446319</t>
         </is>
       </c>
     </row>
@@ -6881,32 +6881,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>14 Jul 2026 - 22:00 (UTC)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Staff scientist (f/m/x) Core Facility Bioinformatics and Statistics</t>
+          <t>PhD Candidate in Agent-Based Modelling and Urban Health: Designing for Movement</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Medical sciences</t>
+          <t>Engineering » Simulation engineering Environmental science » Global change Geography » Human geography Geography » Social geography</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2) First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446270</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446247</t>
         </is>
       </c>
     </row>
@@ -6938,32 +6938,32 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>22 Jul 2026 - 21:59 (UTC)</t>
+          <t>16 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Doctoral student in Physics with a focus on the development of novel X-ray imaging methods with beam-steering ptychography and AI</t>
+          <t>PhD position VIDI project With greater power must come great responsibility</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Juridical sciences » European law Juridical sciences » Informatic law</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446295</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446250</t>
         </is>
       </c>
     </row>
@@ -6995,32 +6995,32 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>14 Jul 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Doctoral student in Physics; Nanoscale X-ray diffraction for ferroelectric domain dynamics</t>
+          <t>Staff scientist (f/m/x) Core Facility Bioinformatics and Statistics</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/446296</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446270</t>
         </is>
       </c>
     </row>
@@ -7047,12 +7047,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>8 Jul 2026 - 21:59 (UTC)</t>
+          <t>22 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7062,22 +7062,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Postdoc in Coupled transport-energy modeling with focus on transport systems</t>
+          <t>Doctoral student in Physics with a focus on the development of novel X-ray imaging methods with beam-steering ptychography and AI</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Engineering » Systems engineering Engineering » Other Technology » Energy technology Technology » Transport technology</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445879</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446295</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18 June 2026</t>
+          <t>19 June 2026</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>15 Sep 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7119,22 +7119,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Postdoc position in AI and Machine Learning for Electromobility</t>
+          <t>Doctoral student in Physics; Nanoscale X-ray diffraction for ferroelectric domain dynamics</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Mathematics » Applied mathematics Technology » Energy technology</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445866</t>
+          <t>https://euraxess.ec.europa.eu/jobs/446296</t>
         </is>
       </c>
     </row>
@@ -7166,12 +7166,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>15 Sep 2026 - 21:59 (UTC)</t>
+          <t>8 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7181,17 +7181,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PhD position in Computational earthquake rupture mechanics</t>
+          <t>Postdoc in Coupled transport-energy modeling with focus on transport systems</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Engineering » Other Environmental science » Earth science Mathematics » Applied mathematics Physics » Applied physics Physics » Computational physics Physics » Other</t>
+          <t>Computer science » Other Engineering » Electrical engineering Engineering » Systems engineering Engineering » Other Technology » Energy technology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445872</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445879</t>
         </is>
       </c>
     </row>
@@ -7223,27 +7223,27 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>29 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Post-Doctoral Researcher in Computational Geomechanics of Gas Migration in Clays</t>
+          <t>Postdoc position in AI and Machine Learning for Electromobility</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Engineering » Civil engineering Engineering » Geological engineering Geosciences » Geology Geosciences » Hydrology</t>
+          <t>Computer science » Other Engineering » Electrical engineering Mathematics » Applied mathematics Technology » Energy technology</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445750</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445866</t>
         </is>
       </c>
     </row>
@@ -7280,32 +7280,32 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Postdoc Position in Cloud and Edge Systems</t>
+          <t>PhD position in Computational earthquake rupture mechanics</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Computer science » Computer systems Computer science » Programming Engineering » Computer engineering Engineering » Systems engineering</t>
+          <t>Engineering » Other Environmental science » Earth science Mathematics » Applied mathematics Physics » Applied physics Physics » Computational physics Physics » Other</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445749</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445872</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>29 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7347,22 +7347,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PhD Universal mechanobiological gateways to Cardiac Regeneration across regenerative and non-regenerative species</t>
+          <t>Post-Doctoral Researcher in Computational Geomechanics of Gas Migration in Clays</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering</t>
+          <t>Engineering » Civil engineering Engineering » Geological engineering Geosciences » Geology Geosciences » Hydrology</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445754</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445750</t>
         </is>
       </c>
     </row>
@@ -7394,32 +7394,32 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>21 Aug 2026 - 21:59 (UTC)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Umeå Stipendier</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Postdoctoral scholarship (2 years) in mid-infrared photothermal microscopy</t>
+          <t>Postdoc Position in Cloud and Edge Systems</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Physics » Applied physics</t>
+          <t>Computer science » Computer systems Computer science » Programming Engineering » Computer engineering Engineering » Systems engineering</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445809</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445749</t>
         </is>
       </c>
     </row>
@@ -7451,27 +7451,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>21 Aug 2026 - 12:00 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Talentech</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PhD student in generative modeling for data-efficient machine learning</t>
+          <t>PhD Universal mechanobiological gateways to Cardiac Regeneration across regenerative and non-regenerative species</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Computer science</t>
+          <t>Engineering » Biomedical engineering</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445739</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445754</t>
         </is>
       </c>
     </row>
@@ -7503,32 +7503,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>23 Jul 2026 - 21:59 (UTC)</t>
+          <t>21 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Maastricht University via AcademicTransfer</t>
+          <t>Umeå Stipendier</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PhD Candidate in Mass Spectrometry Instrumentation</t>
+          <t>Postdoctoral scholarship (2 years) in mid-infrared photothermal microscopy</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Physics » Applied physics</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445398</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445809</t>
         </is>
       </c>
     </row>
@@ -7560,37 +7560,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>17 June 2026</t>
+          <t>18 June 2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>14 Jul 2026 - 21:59 (UTC)</t>
+          <t>21 Aug 2026 - 12:00 (UTC)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Talentech</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Postdoc - Design of Experiment and Digital Process Optimization for CO2 Electrolysis</t>
+          <t>PhD student in generative modeling for data-efficient machine learning</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Computer science</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445415</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445739</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>19 Jul 2026 - 21:59 (UTC)</t>
+          <t>23 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Maastricht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PhD Position in Extended Reality for Safe and Active Mobility</t>
+          <t>PhD Candidate in Mass Spectrometry Instrumentation</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Engineering » Civil engineering Engineering » Computer engineering</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445389</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445398</t>
         </is>
       </c>
     </row>
@@ -7679,32 +7679,32 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>19 Jul 2026 - 21:59 (UTC)</t>
+          <t>14 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PhD Position in Data and AI for Multi-Source Micromobility Safety Analytics</t>
+          <t>Postdoc - Design of Experiment and Digital Process Optimization for CO2 Electrolysis</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Engineering » Civil engineering Engineering » Computer engineering</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445390</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445415</t>
         </is>
       </c>
     </row>
@@ -7736,27 +7736,27 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>17 Aug 2026 - 21:59 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Uppsala Universitet via MyNetwork</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Doctoral (Phd) position in Tribology with focus on Sustainable transformer oils for electrical contacts</t>
+          <t>PhD Position in Extended Reality for Safe and Active Mobility</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering</t>
+          <t>Engineering » Civil engineering Engineering » Computer engineering</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445381</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445389</t>
         </is>
       </c>
     </row>
@@ -7793,32 +7793,32 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>9 Aug 2026 - 21:59 (UTC)</t>
+          <t>19 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Jönköpings University</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Assistant Professor or Senior Associate Lecturer with a focus on Automation</t>
+          <t>PhD Position in Data and AI for Multi-Source Micromobility Safety Analytics</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering » Civil engineering Engineering » Computer engineering</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Virtual Sensor</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445379</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445390</t>
         </is>
       </c>
     </row>
@@ -7850,27 +7850,27 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1 Aug 2026 - 17:00 (Europe/Zurich)</t>
+          <t>17 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HES-SO Genève</t>
+          <t>Uppsala Universitet via MyNetwork</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PhD position in applied research - Dynamic risk assessment for Critical Infrastructure Security</t>
+          <t>Doctoral (Phd) position in Tribology with focus on Sustainable transformer oils for electrical contacts</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Computer science » Other</t>
+          <t>Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445626</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445381</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>9 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7917,22 +7917,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Jönköpings University</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Doctoral student in Computer Science with a focus on Human-Swarm Interaction and Adaptive Swarm Teamwork</t>
+          <t>Assistant Professor or Senior Associate Lecturer with a focus on Automation</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Other</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Virtual Sensor</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445460</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445379</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>14 Sep 2026 - 21:59 (UTC)</t>
+          <t>1 Aug 2026 - 17:00 (Europe/Zurich)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7974,17 +7974,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>HES-SO Genève</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PhD Position in AI-Supported Resilience Assessment of Climate-Neutral Transport Infrastructure</t>
+          <t>PhD position in applied research - Dynamic risk assessment for Critical Infrastructure Security</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Civil engineering Engineering » Other Environmental science » Earth science Technology » Environmental technology Technology » Transport technology</t>
+          <t>Computer science » Other</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445465</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445626</t>
         </is>
       </c>
     </row>
@@ -8021,27 +8021,27 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>12 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Maastricht University via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PhD Position in Neuro-Musculoskeletal Cell-Materials Atlas</t>
+          <t>Doctoral student in Computer Science with a focus on Human-Swarm Interaction and Adaptive Swarm Teamwork</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Biological sciences » Biology Engineering » Biomaterial engineering Engineering » Biomedical engineering</t>
+          <t>Computer science » Other Engineering » Other</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445385</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445460</t>
         </is>
       </c>
     </row>
@@ -8078,32 +8078,32 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>14 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Postdoc Superconducting Single Photon Detector Arrays for Imaging</t>
+          <t>PhD Position in AI-Supported Resilience Assessment of Climate-Neutral Transport Infrastructure</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Microengineering Physics » Optics Physics » Quantum mechanics</t>
+          <t>Computer science » Other Engineering » Civil engineering Engineering » Other Environmental science » Earth science Technology » Environmental technology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445387</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445465</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>12 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8145,17 +8145,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Maastricht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>PhD Position on Thin Film Energy Materials</t>
+          <t>PhD Position in Neuro-Musculoskeletal Cell-Materials Atlas</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Engineering » Chemical engineering Engineering » Materials engineering</t>
+          <t>Biological sciences » Biology Engineering » Biomaterial engineering Engineering » Biomedical engineering</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445392</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445385</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>28 Jul 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Postdoc Scalable Graph Learning</t>
+          <t>Postdoc Superconducting Single Photon Detector Arrays for Imaging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Computer science » Programming</t>
+          <t>Engineering » Electrical engineering Engineering » Microengineering Physics » Optics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445393</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445387</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>1 Aug 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8259,22 +8259,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Wageningen University and Research Centre via AcademicTransfer</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lecturer in Big Data and Artificial Intelligence</t>
+          <t>PhD Position on Thin Film Energy Materials</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Computer science » Database management Computer science » Programming</t>
+          <t>Engineering » Chemical engineering Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445395</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445392</t>
         </is>
       </c>
     </row>
@@ -8306,32 +8306,32 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:14 (UTC)</t>
+          <t>28 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Postdoc or PhD Candidate (f/m/x) - AI Augmented Target Discovery in Translational Kidney Disease</t>
+          <t>Postdoc Scalable Graph Learning</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Medical sciences</t>
+          <t>Computer science » Informatics Computer science » Programming</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445411</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445393</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8358,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>16 June 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>20 Jul 2026 - 21:59 (UTC)</t>
+          <t>1 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Wageningen University and Research Centre via AcademicTransfer</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>PhD in Quantum Algorithms for Chemistry</t>
+          <t>Lecturer in Big Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chemistry » Computational chemistry Chemistry » Physical chemistry Computer science » Informatics Computer science » Programming Physics » Computational physics Physics » Quantum mechanics</t>
+          <t>Computer science » Database management Computer science » Programming</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445028</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445395</t>
         </is>
       </c>
     </row>
@@ -8415,37 +8415,37 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>16 June 2026</t>
+          <t>17 June 2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>18 Aug 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:14 (UTC)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>EngD in Data Interaction for Remote Heart Failure Monitoring</t>
+          <t>Postdoc or PhD Candidate (f/m/x) - AI Augmented Target Discovery in Translational Kidney Disease</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Computer science » Systems design Engineering » Biomedical engineering Engineering » Systems engineering</t>
+          <t>Medical sciences</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445023</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445411</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1 Jul 2026 - 21:59 (UTC)</t>
+          <t>20 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8487,22 +8487,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Erasmus University Rotterdam via AcademicTransfer</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher - EU Horizon Projects</t>
+          <t>PhD in Quantum Algorithms for Chemistry</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Communication sciences » Media studies Sociology » Social shaping of technology Sociology » Sociology of labour</t>
+          <t>Chemistry » Computational chemistry Chemistry » Physical chemistry Computer science » Informatics Computer science » Programming Physics » Computational physics Physics » Quantum mechanics</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445026</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445028</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>15 Jul 2026 - 21:59 (UTC)</t>
+          <t>18 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8544,22 +8544,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PhD Position Microclimate Adaptive Grid CFD Modeling</t>
+          <t>EngD in Data Interaction for Remote Heart Failure Monitoring</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Agronomics Agricultural sciences » Phytotechny Engineering » Civil engineering Engineering » Mechanical engineering</t>
+          <t>Computer science » Informatics Computer science » Systems design Engineering » Biomedical engineering Engineering » Systems engineering</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/445031</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445023</t>
         </is>
       </c>
     </row>
@@ -8586,12 +8586,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>16 June 2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>15 Aug 2026 - 21:59 (UTC)</t>
+          <t>1 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8601,22 +8601,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Erasmus University Rotterdam via AcademicTransfer</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Assistant Professors in Mission-Driven Research on Future-Proof Networks</t>
+          <t>Postdoctoral Researcher - EU Horizon Projects</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Mathematics » Discrete mathematics Mathematics » Probability theory Mathematics » Statistics</t>
+          <t>Communication sciences » Media studies Sociology » Social shaping of technology Sociology » Sociology of labour</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/436378</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445026</t>
         </is>
       </c>
     </row>
@@ -8643,32 +8643,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>14 June 2026</t>
+          <t>16 June 2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Doctoral student in Physics within AI-accelerated AlN MOCVD growth</t>
+          <t>PhD Position Microclimate Adaptive Grid CFD Modeling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Agricultural sciences » Agronomics Agricultural sciences » Phytotechny Engineering » Civil engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444805</t>
+          <t>https://euraxess.ec.europa.eu/jobs/445031</t>
         </is>
       </c>
     </row>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>14 June 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>12 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8715,22 +8715,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wageningen University and Research Centre via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Researcher in Fish Physiology</t>
+          <t>Assistant Professors in Mission-Driven Research on Future-Proof Networks</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Agricultural sciences » Zootechnics Biological sciences » Nutritional sciences Biological sciences » Zoology</t>
+          <t>Mathematics » Discrete mathematics Mathematics » Probability theory Mathematics » Statistics</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444799</t>
+          <t>https://euraxess.ec.europa.eu/jobs/436378</t>
         </is>
       </c>
     </row>
@@ -8757,37 +8757,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>14 June 2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>18 Jul 2026 - 22:00 (UTC)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ABG  - Association Bernard Gregory</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>NCCR Clim+: PhD Water and Agriculture</t>
+          <t>Doctoral student in Physics within AI-accelerated AlN MOCVD growth</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Environmental science » Ecology Agricultural sciences » Agronomics Geography</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Leading Researcher (R4) First Stage Researcher (R1) Established Researcher (R3)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/435811</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444805</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>14 June 2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>9 Jul 2026 - 21:59 (UTC)</t>
+          <t>12 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8829,17 +8829,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Wageningen University and Research Centre via AcademicTransfer</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>(Junior) Researcher</t>
+          <t>Researcher in Fish Physiology</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Engineering » Biomaterial engineering Engineering » Materials engineering</t>
+          <t>Agricultural sciences » Zootechnics Biological sciences » Nutritional sciences Biological sciences » Zoology</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444640</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444799</t>
         </is>
       </c>
     </row>
@@ -8871,37 +8871,37 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>13 June 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>28 Jun 2026 - 21:59 (UTC)</t>
+          <t>18 Jul 2026 - 22:00 (UTC)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>ABG  - Association Bernard Gregory</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Junior lecturer in Energy Sciences</t>
+          <t>NCCR Clim+: PhD Water and Agriculture</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Engineering » Thermal engineering Environmental science » Global change Environmental science » Natural resources management</t>
+          <t>Environmental science » Ecology Agricultural sciences » Agronomics Geography</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2) Leading Researcher (R4) Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2) Leading Researcher (R4) First Stage Researcher (R1) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444653</t>
+          <t>https://euraxess.ec.europa.eu/jobs/435811</t>
         </is>
       </c>
     </row>
@@ -8933,32 +8933,32 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>9 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>PhD Position - Control System for the Climate-Neutral Operation of the Einstein Telescope's Computing Centre</t>
+          <t>(Junior) Researcher</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Engineering » Biomaterial engineering Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444669</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444640</t>
         </is>
       </c>
     </row>
@@ -8990,32 +8990,32 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>10 Jul 2026 - 21:59 (UTC)</t>
+          <t>28 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>PhD on Hydrological model-data interaction and machine learning for headwater catchment analyses</t>
+          <t>Junior lecturer in Energy Sciences</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Computer science » Other Environmental science » Earth science Environmental science » Other</t>
+          <t>Engineering » Thermal engineering Environmental science » Global change Environmental science » Natural resources management</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2) Leading Researcher (R4) Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444752</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444653</t>
         </is>
       </c>
     </row>
@@ -9047,27 +9047,27 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>PhD Position Structural Biology of the Neuronal Synapse</t>
+          <t>PhD Position - Control System for the Climate-Neutral Operation of the Einstein Telescope's Computing Centre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Neurosciences » Neurobiology Neurosciences » Neurochemistry</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444634</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444669</t>
         </is>
       </c>
     </row>
@@ -9104,27 +9104,27 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>31 Aug 2026 - 15:37 (UTC)</t>
+          <t>10 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Helmholtz Association of German Research Centres</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>PhD Position - Generative AI for Smart Grids and Energy Systems</t>
+          <t>PhD on Hydrological model-data interaction and machine learning for headwater catchment analyses</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Computer science » Other Environmental science » Earth science Environmental science » Other</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444670</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444752</t>
         </is>
       </c>
     </row>
@@ -9161,27 +9161,27 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>16 Aug 2026 - 21:59 (UTC)</t>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Doctoral student in statistical shape modelling of the human body for vehicle safety applications</t>
+          <t>PhD Position Structural Biology of the Neuronal Synapse</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other Mathematics » Statistics Medical sciences » Other Physics » Other</t>
+          <t>Neurosciences » Neurobiology Neurosciences » Neurochemistry</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444767</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444634</t>
         </is>
       </c>
     </row>
@@ -9218,32 +9218,32 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Aug 2026 - 15:37 (UTC)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Helmholtz Association of German Research Centres</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Postdoc in Trustworthy AI for Localization and Sensing</t>
+          <t>PhD Position - Generative AI for Smart Grids and Energy Systems</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Communication engineering Engineering » Other Mathematics » Probability theory Mathematics » Statistics</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444768</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444670</t>
         </is>
       </c>
     </row>
@@ -9275,27 +9275,27 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>11 Jul 2026 - 21:59 (UTC)</t>
+          <t>16 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>PhD in Process-Aware AI Agents for Autonomous Manufacturing at Process Analytics Cluster</t>
+          <t>Doctoral student in statistical shape modelling of the human body for vehicle safety applications</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Computer science » Programming Engineering » Industrial engineering Engineering » Process engineering</t>
+          <t>Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other Mathematics » Statistics Medical sciences » Other Physics » Other</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Automotive AI</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444646</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444767</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>12 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9342,17 +9342,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Post-doctoral fellow in Physics; fast time-resolved 3D imaging with X-ray multi-projection imaging for advanced manufacturing</t>
+          <t>Postdoc in Trustworthy AI for Localization and Sensing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Computer science » Other Engineering » Communication engineering Engineering » Other Mathematics » Probability theory Mathematics » Statistics</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9367,12 +9367,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444730</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444768</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>PhD in Active Inference for Manufacturing Processes</t>
+          <t>PhD in Process-Aware AI Agents for Autonomous Manufacturing at Process Analytics Cluster</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering Engineering » Industrial engineering</t>
+          <t>Computer science » Informatics Computer science » Programming Engineering » Industrial engineering Engineering » Process engineering</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Physics-informed</t>
+          <t>Automotive AI</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444648</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444646</t>
         </is>
       </c>
     </row>
@@ -9446,32 +9446,32 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>11 Jul 2026 - 21:59 (UTC)</t>
+          <t>12 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>PhD in AI for reconfigurable robot collectives and real-time flow control</t>
+          <t>Post-doctoral fellow in Physics; fast time-resolved 3D imaging with X-ray multi-projection imaging for advanced manufacturing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Computer science » Cybernetics Computer science » Programming Engineering » Control engineering Engineering » Mechanical engineering</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Model Predictive Control</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444649</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444730</t>
         </is>
       </c>
     </row>
@@ -9503,27 +9503,27 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>13 Jul 2026 - 21:59 (UTC)</t>
+          <t>11 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Doctoral Student in Human-in-the-Loop Autonomous Systems</t>
+          <t>PhD in Active Inference for Manufacturing Processes</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other Engineering » Control engineering Engineering » Other</t>
+          <t>Engineering » Electrical engineering Engineering » Industrial engineering</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Physics-informed</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444766</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444648</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>15 Sep 2026 - 21:59 (UTC)</t>
+          <t>11 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Three fully funded PhD positions in Competition Law and AI</t>
+          <t>PhD in AI for reconfigurable robot collectives and real-time flow control</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Computer science » Informatics Juridical sciences » European law Juridical sciences » Informatic law</t>
+          <t>Computer science » Cybernetics Computer science » Programming Engineering » Control engineering Engineering » Mechanical engineering</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Model Predictive Control</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444655</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444649</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2 Jul 2026 - 21:59 (UTC)</t>
+          <t>13 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9627,17 +9627,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Doctoral student in Biophysical Chemistry and Protein Self-Assembly</t>
+          <t>Doctoral Student in Human-in-the-Loop Autonomous Systems</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Computer science » Programming Computer science » Other Engineering » Control engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444731</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444766</t>
         </is>
       </c>
     </row>
@@ -9674,27 +9674,27 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>21 Jun 2026 - 21:59 (UTC)</t>
+          <t>15 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Research Engineer in Machine Learning and Health Data</t>
+          <t>Three fully funded PhD positions in Competition Law and AI</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other</t>
+          <t>Computer science » Informatics Juridical sciences » European law Juridical sciences » Informatic law</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Applied AI</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444755</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444655</t>
         </is>
       </c>
     </row>
@@ -9726,12 +9726,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>12 June 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>16 Aug 2026 - 21:59 (UTC)</t>
+          <t>2 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9741,22 +9741,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Lund University via MyNetwork</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Postdoc in Sodium-ion batteries for transport: from materials to cell performance</t>
+          <t>Doctoral student in Biophysical Chemistry and Protein Self-Assembly</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chemistry » Other Engineering » Chemical engineering Engineering » Electrical engineering Engineering » Materials engineering Engineering » Other Technology » Energy technology</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Battery Management</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444376</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444731</t>
         </is>
       </c>
     </row>
@@ -9783,32 +9783,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>12 June 2026</t>
+          <t>13 June 2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>29 Jun 2026 - 21:59 (UTC)</t>
+          <t>21 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PhD Position Socio-Economic Modelling of Nature Restoration at European scale</t>
+          <t>Research Engineer in Machine Learning and Health Data</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Economics » Applied economics Economics » Environmental economics Environmental science » Ecology Environmental science » Natural resources management</t>
+          <t>Computer science » Programming Computer science » Other</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Applied AI</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444237</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444755</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>15 Aug 2026 - 21:59 (UTC)</t>
+          <t>16 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Postdoc in Modeling of Human-like Balance and Step Recovery</t>
+          <t>Postdoc in Sodium-ion batteries for transport: from materials to cell performance</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other Technology » Transport technology</t>
+          <t>Chemistry » Other Engineering » Chemical engineering Engineering » Electrical engineering Engineering » Materials engineering Engineering » Other Technology » Energy technology</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Battery Management</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444375</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444376</t>
         </is>
       </c>
     </row>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>9 Jul 2026 - 21:59 (UTC)</t>
+          <t>29 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9912,22 +9912,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Postdoc Advanced Ultrasound Arrays Technology</t>
+          <t>PhD Position Socio-Economic Modelling of Nature Restoration at European scale</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Engineering » Biomedical engineering Engineering » Electrical engineering</t>
+          <t>Economics » Applied economics Economics » Environmental economics Environmental science » Ecology Environmental science » Natural resources management</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Soft Sensor</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444239</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444237</t>
         </is>
       </c>
     </row>
@@ -9959,27 +9959,27 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>6 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Postdoc Surface Water Salinity Intrusion in the Ganges-Brahmaputra-Meghna Delta</t>
+          <t>Postdoc in Modeling of Human-like Balance and Step Recovery</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Engineering » Civil engineering Engineering » Water resources engineering Environmental science » Water science</t>
+          <t>Computer science » Other Engineering » Biomedical engineering Engineering » Control engineering Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other Technology » Transport technology</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444232</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444375</t>
         </is>
       </c>
     </row>
@@ -10011,37 +10011,37 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>12 June 2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 23:59 (Europe/Berlin)</t>
+          <t>9 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Constructor University Bremen gGmbH</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Assistant / Associate Professor of Biotechnology (m/f/d)</t>
+          <t>Postdoc Advanced Ultrasound Arrays Technology</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Technology » Biotechnology</t>
+          <t>Engineering » Biomedical engineering Engineering » Electrical engineering</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Data-driven Control</t>
+          <t>Soft Sensor</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/435218</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444239</t>
         </is>
       </c>
     </row>
@@ -10068,37 +10068,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>12 June 2026</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>28 Jul 2026 - 23:59 (Europe/Berlin)</t>
+          <t>6 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Brandenburgische Technische Universität Cottbus</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>PROFESSORSHIP (W3) Aerospace Propulsion Technology (Luftfahrtantriebe)</t>
+          <t>Postdoc Surface Water Salinity Intrusion in the Ganges-Brahmaputra-Meghna Delta</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Engineering » Other Physics » Other</t>
+          <t>Engineering » Civil engineering Engineering » Water resources engineering Environmental science » Water science</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Established Researcher (R3)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444058</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444232</t>
         </is>
       </c>
     </row>
@@ -10125,37 +10125,37 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>24 Jun 2026 - 21:59 (UTC)</t>
+          <t>30 Jun 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Delft University of Technology via AcademicTransfer</t>
+          <t>Constructor University Bremen gGmbH</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>PhD Position Packaging Solutions</t>
+          <t>Assistant / Associate Professor of Biotechnology (m/f/d)</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Engineering » Electronic engineering Engineering » Materials engineering</t>
+          <t>Technology » Biotechnology</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Data-driven Control</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443845</t>
+          <t>https://euraxess.ec.europa.eu/jobs/435218</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 00:00 (Europe/Berlin)</t>
+          <t>28 Jul 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10197,22 +10197,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Leibniz Institute of Vegetable and Ornamental Crops</t>
+          <t>Brandenburgische Technische Universität Cottbus</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>PhD student (f,m,div) in Plant Biology</t>
+          <t>PROFESSORSHIP (W3) Aerospace Propulsion Technology (Luftfahrtantriebe)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Biological sciences » Biology</t>
+          <t>Engineering » Other Physics » Other</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Established Researcher (R3)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/444197</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444058</t>
         </is>
       </c>
     </row>
@@ -10244,32 +10244,32 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>7 Sep 2026 - 21:59 (UTC)</t>
+          <t>24 Jun 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Delft University of Technology via AcademicTransfer</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher - Bone Organoids</t>
+          <t>PhD Position Packaging Solutions</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Biological sciences » Other Engineering » Biomedical engineering Physics » Biophysics Technology » Biotechnology</t>
+          <t>Engineering » Electronic engineering Engineering » Materials engineering</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443947</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443845</t>
         </is>
       </c>
     </row>
@@ -10301,27 +10301,27 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>11 Aug 2026 - 21:59 (UTC)</t>
+          <t>5 Jul 2026 - 00:00 (Europe/Berlin)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>Leibniz Institute of Vegetable and Ornamental Crops</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Doctoral student in Resilient and Equitable Mobility Systems</t>
+          <t>PhD student (f,m,div) in Plant Biology</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Computer science » Programming Computer science » Other Environmental science » Earth science Mathematics » Applied mathematics Sociology » Urban sociology Technology » Transport technology</t>
+          <t>Biological sciences » Biology</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443957</t>
+          <t>https://euraxess.ec.europa.eu/jobs/444197</t>
         </is>
       </c>
     </row>
@@ -10358,12 +10358,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>11 Aug 2026 - 21:59 (UTC)</t>
+          <t>7 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Postdoc in Resilient and Equitable Mobility Systems</t>
+          <t>Postdoctoral Researcher - Bone Organoids</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Computer science » Other Environmental science » Earth science Geography » Other Mathematics » Applied mathematics Sociology » Urban sociology Technology » Transport technology</t>
+          <t>Biological sciences » Other Engineering » Biomedical engineering Physics » Biophysics Technology » Biotechnology</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443958</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443947</t>
         </is>
       </c>
     </row>
@@ -10415,32 +10415,32 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9 Jul 2026 - 21:59 (UTC)</t>
+          <t>11 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Postdoc on human-centric, collaborative AI</t>
+          <t>Doctoral student in Resilient and Equitable Mobility Systems</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Computer science » Cybernetics Computer science » Programming</t>
+          <t>Computer science » Programming Computer science » Other Environmental science » Earth science Mathematics » Applied mathematics Sociology » Urban sociology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443852</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443957</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>31 Jul 2026 - 21:59 (UTC)</t>
+          <t>11 Aug 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10482,17 +10482,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Umeå Stipendier</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Postdoctoral scholarship (2 years) within Optimization and Learning for Distributed Decision Systems</t>
+          <t>Postdoc in Resilient and Equitable Mobility Systems</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Mathematics » Statistics</t>
+          <t>Computer science » Other Environmental science » Earth science Geography » Other Mathematics » Applied mathematics Sociology » Urban sociology Technology » Transport technology</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443888</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443958</t>
         </is>
       </c>
     </row>
@@ -10534,22 +10534,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Postdoc in Quality-Aware Machine Learning and AI Systems</t>
+          <t>Postdoc on human-centric, collaborative AI</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Computer science » Other Mathematics » Statistics</t>
+          <t>Computer science » Cybernetics Computer science » Programming</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Domain Adaptation</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443955</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443852</t>
         </is>
       </c>
     </row>
@@ -10586,27 +10586,27 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>15 Jul 2026 - 21:59 (UTC)</t>
+          <t>31 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Utrecht University via AcademicTransfer</t>
+          <t>Umeå Stipendier</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher for Data Analysis</t>
+          <t>Postdoctoral scholarship (2 years) within Optimization and Learning for Distributed Decision Systems</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Geosciences » Geology</t>
+          <t>Mathematics » Statistics</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443846</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443888</t>
         </is>
       </c>
     </row>
@@ -10643,27 +10643,27 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>24 Jul 2026 - 21:59 (UTC)</t>
+          <t>9 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Postdoc in geopolitics and governance of chip security value chains</t>
+          <t>Postdoc in Quality-Aware Machine Learning and AI Systems</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Geography » Geopolitics</t>
+          <t>Computer science » Other Mathematics » Statistics</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443848</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443955</t>
         </is>
       </c>
     </row>
@@ -10695,12 +10695,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>10 June 2026</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>5 Jul 2026 - 21:59 (UTC)</t>
+          <t>15 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10710,22 +10710,22 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Utrecht University via AcademicTransfer</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>PhD position in multi-material additive manufacturing for advanced chip cooling</t>
+          <t>Postdoctoral Researcher for Data Analysis</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Thermal engineering</t>
+          <t>Geosciences » Geology</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10735,12 +10735,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Thermal Management</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443575</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443846</t>
         </is>
       </c>
     </row>
@@ -10752,37 +10752,37 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>10 June 2026</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>6 Sep 2026 - 21:59 (UTC)</t>
+          <t>24 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Academic Positions</t>
+          <t>University of Amsterdam (UvA) via AcademicTransfer</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>PhD position in Soft Robotics Systems</t>
+          <t>Postdoc in geopolitics and governance of chip security value chains</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Computer science » Other Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other</t>
+          <t>Geography » Geopolitics</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>First Stage Researcher (R1)</t>
+          <t>Recognised Researcher (R2)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Climate Control</t>
+          <t>Explainable AI</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443648</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443848</t>
         </is>
       </c>
     </row>
@@ -10814,32 +10814,32 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>29 Jun 2026 - 21:59 (UTC)</t>
+          <t>5 Jul 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lund University via MyNetwork</t>
+          <t>AcademicTransfer</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Postdoctoral position in Electrical Engineering focusing on Machine Learning</t>
+          <t>PhD position in multi-material additive manufacturing for advanced chip cooling</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Engineering » Electrical engineering</t>
+          <t>Engineering » Materials engineering Engineering » Mechanical engineering Engineering » Thermal engineering</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Recognised Researcher (R2)</t>
+          <t>First Stage Researcher (R1)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Domain Adaptation</t>
+          <t>Thermal Management</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443632</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443575</t>
         </is>
       </c>
     </row>
@@ -10871,27 +10871,27 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>30 Jun 2026 - 21:59 (UTC)</t>
+          <t>6 Sep 2026 - 21:59 (UTC)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AcademicTransfer</t>
+          <t>Academic Positions</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>PhD position for NWO project ECHoFAIR: empowering collaborative human-AI teaming for failure analysis and intelligent risk a...</t>
+          <t>PhD position in Soft Robotics Systems</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Computer science » Cybernetics Computer science » Informatics Engineering » Industrial engineering Engineering » Systems engineering</t>
+          <t>Computer science » Other Engineering » Electrical engineering Engineering » Mechanical engineering Engineering » Other</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Explainable AI</t>
+          <t>Climate Control</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://euraxess.ec.europa.eu/jobs/443574</t>
+          <t>https://euraxess.ec.europa.eu/jobs/443648</t>
         </is>
       </c>
     </row>
@@ -10923,50 +10923,164 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
+          <t>10 June 2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>29 Jun 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Lund University via MyNetwork</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Postdoctoral position in Electrical Engineering focusing on Machine Learning</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Engineering » Electrical engineering</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Recognised Researcher (R2)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Domain Adaptation</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443632</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>10 June 2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>30 Jun 2026 - 21:59 (UTC)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AcademicTransfer</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>PhD position for NWO project ECHoFAIR: empowering collaborative human-AI teaming for failure analysis and intelligent risk a...</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Computer science » Cybernetics Computer science » Informatics Engineering » Industrial engineering Engineering » Systems engineering</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>First Stage Researcher (R1)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Explainable AI</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/443574</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
           <t>1 June 2026</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>31 Jul 2026 - 23:59 (Europe/Berlin)</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>University of Bremen</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>2 independent postdoctoral researchers (f/m/d) - The Martian Mindset Open Idea Competition</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="H187" t="inlineStr">
         <is>
           <t>Recognised Researcher (R2)</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
         <is>
           <t>Explainable AI</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="K187" t="inlineStr">
         <is>
           <t>https://euraxess.ec.europa.eu/jobs/441376</t>
         </is>
